--- a/providers/xtrackers/2026-06-23/xtrackers_etf_export.xlsx
+++ b/providers/xtrackers/2026-06-23/xtrackers_etf_export.xlsx
@@ -24599,441 +24599,441 @@
     <x:mergeCell ref="B438:R438"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink ref="B8:B8" r:id="R6e1bdefad5c748a7" display="https://etf.dws.com//en-gb/IE00002ZKAP0-europe-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B9:B9" r:id="R15da2837f67c4095" display="https://etf.dws.com//en-gb/IE00004DJ199-msci-world-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B10:B10" r:id="R51321ff3efd8484d" display="https://etf.dws.com//en-gb/IE0000K7HU41-msci-usa-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B11:B11" r:id="R042dc2d64caf477a" display="https://etf.dws.com//en-gb/IE0000MMQ5M5-msci-usa-esg-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B12:B12" r:id="R46cfd74fe8a844ae" display="https://etf.dws.com//en-gb/IE0001JH5CB4-europe-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B13:B13" r:id="Rb7406aa68eac4cb6" display="https://etf.dws.com//en-gb/IE0001TLQX55-s-p-500-garp-ucits-etf-1c/"/>
-    <x:hyperlink ref="B14:B14" r:id="Rc8a4dcf8186c4825" display="https://etf.dws.com//en-gb/IE00028H9QJ8-usd-corporate-green-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B15:B15" r:id="R94b5c37f8a75440f" display="https://etf.dws.com//en-gb/IE0002EI5AG0-s-p-500-equal-weight-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B16:B16" r:id="Rb3e621e196734be5" display="https://etf.dws.com//en-gb/IE0002GFATQ6-s-p-500-equal-weight-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B17:B17" r:id="R70549793cb414802" display="https://etf.dws.com//en-gb/IE0002PGSLZ5-us-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B18:B18" r:id="R0b45c13dbd574b8f" display="https://etf.dws.com//en-gb/IE0002ZM3JI1-usa-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B19:B19" r:id="R334fdb83ba11418f" display="https://etf.dws.com//en-gb/IE00036F4K40-msci-global-sdg-3-good-health-ucits-etf-1c/"/>
-    <x:hyperlink ref="B20:B20" r:id="Rc1c606f084114dd4" display="https://etf.dws.com//en-gb/IE0003NQ0IY5-msci-world-quality-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B21:B21" r:id="R3e27b7210cc84536" display="https://etf.dws.com//en-gb/IE0003W9O921-usd-corporate-green-bond-ucits-etf-2c/"/>
-    <x:hyperlink ref="B22:B22" r:id="R455e4be3544b4962" display="https://etf.dws.com//en-gb/IE000472H9T4-nasdaq-100-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B23:B23" r:id="Rddf9468942ff4241" display="https://etf.dws.com//en-gb/IE0004KLW911-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1c/"/>
-    <x:hyperlink ref="B24:B24" r:id="R5cf017173c724d19" display="https://etf.dws.com//en-gb/IE0004MFRED4-s-p-500-equal-weight-scored-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B25:B25" r:id="R6eaa11baee8a4e66" display="https://etf.dws.com//en-gb/IE0004ZJGWT9-msci-europe-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B26:B26" r:id="R1ab584512ee742a3" display="https://etf.dws.com//en-gb/IE0005E47AH7-msci-global-sdg-9-industry-innovation-infrastructure-ucits-etf-1c/"/>
-    <x:hyperlink ref="B27:B27" r:id="R050f85e2454c4473" display="https://etf.dws.com//en-gb/IE0006FDYJF8-msci-japan-climate-transition-ucits-etf-1d/"/>
-    <x:hyperlink ref="B28:B28" r:id="R37f6795ced084050" display="https://etf.dws.com//en-gb/IE0006FFX5U1-msci-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B29:B29" r:id="R0acf4106bc3741bc" display="https://etf.dws.com//en-gb/IE0006GNB732-eur-high-yield-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B30:B30" r:id="R0cd2d6ba7d2d4917" display="https://etf.dws.com//en-gb/IE0006I3NZF8-msci-usa-consumer-discretionary-ucits-etf-1c/"/>
-    <x:hyperlink ref="B31:B31" r:id="R469a5faf9097456f" display="https://etf.dws.com//en-gb/IE0006WW1TQ4-msci-world-ex-usa-ucits-etf-1c/"/>
-    <x:hyperlink ref="B32:B32" r:id="R34fa432d1fbd47bc" display="https://etf.dws.com//en-gb/IE0006YM7D84-usd-high-yield-corporate-bond-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B33:B33" r:id="Rd3b8f034a6734772" display="https://etf.dws.com//en-gb/IE00074JLU02-japan-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B34:B34" r:id="R0ca852eb0ad74ac0" display="https://etf.dws.com//en-gb/IE0007ULOZS8-s-p-500-scored-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B35:B35" r:id="Rea8c60882c43496c" display="https://etf.dws.com//en-gb/IE0007WJ6B10-msci-global-clean-water-sanitation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B36:B36" r:id="R72a5835f483649c1" display="https://etf.dws.com//en-gb/IE0008YN0OY8-msci-world-minimum-volatility-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B37:B37" r:id="Rd829d6ee71c44283" display="https://etf.dws.com//en-gb/IE00094GSCQ4-world-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B38:B38" r:id="R191856faca1b4b5e" display="https://etf.dws.com//en-gb/IE0009KLWT21-msci-world-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B39:B39" r:id="Rbe35998795184496" display="https://etf.dws.com//en-gb/IE000BO2Y0T8-msci-nordic-ucits-etf-1c/"/>
-    <x:hyperlink ref="B40:B40" r:id="Rea4e3e9884eb443c" display="https://etf.dws.com//en-gb/IE000CXLGK86-s-p-500-equal-weight-ucits-etf-2d/"/>
-    <x:hyperlink ref="B41:B41" r:id="R44a33a5441df4278" display="https://etf.dws.com//en-gb/IE000DNSAS54-msci-emerging-markets-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B42:B42" r:id="Rf572ed5b8fa44d17" display="https://etf.dws.com//en-gb/IE000DVHJV46-s-p-500-market-leaders-ucits-etf-1c/"/>
-    <x:hyperlink ref="B43:B43" r:id="R4a216aac77fa41c0" display="https://etf.dws.com//en-gb/IE000E0V65D8-world-biodiversity-focus-sri-ucits-etf-1c/"/>
-    <x:hyperlink ref="B44:B44" r:id="Rb69f6c88f08b4945" display="https://etf.dws.com//en-gb/IE000E4BATC9-msci-world-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B45:B45" r:id="R21dfe849815047fe" display="https://etf.dws.com//en-gb/IE000ER61U30-msci-europe-small-cap-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B46:B46" r:id="Reb12f30681c34bfa" display="https://etf.dws.com//en-gb/IE000EVOVOG1-msci-usa-positioning-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B47:B47" r:id="R9ddc3a1e30394c51" display="https://etf.dws.com//en-gb/IE000EXUE0G2-nasdaq-100-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B48:B48" r:id="Rae6badb5e7974a6c" display="https://etf.dws.com//en-gb/IE000F04HGE5-floating-rate-notes-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B49:B49" r:id="Ra3fbff66f34243f6" display="https://etf.dws.com//en-gb/IE000F354Q61-msci-world-small-cap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B50:B50" r:id="R027851eeaaad4a0a" display="https://etf.dws.com//en-gb/IE000FL46JJ1-s-p-500-equal-weight-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B51:B51" r:id="Rf312703246db4cd7" display="https://etf.dws.com//en-gb/IE000FO05UG4-s-p-500-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B52:B52" r:id="Rcd045361f0b94891" display="https://etf.dws.com//en-gb/IE000FO1A5D1-s-p-500-equal-weight-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B53:B53" r:id="Rf77d9656b9ec471a" display="https://etf.dws.com//en-gb/IE000FW16TX1-msci-usa-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B54:B54" r:id="R6a0364d9f6644020" display="https://etf.dws.com//en-gb/IE000GF6QTP6-s-p-500-equal-weight-scored-screened-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B55:B55" r:id="Rbf90744ee8e149a5" display="https://etf.dws.com//en-gb/IE000GWA2J58-msci-emerging-markets-ucits-etf-1d/"/>
-    <x:hyperlink ref="B56:B56" r:id="Rda7c4c04228f4721" display="https://etf.dws.com//en-gb/IE000GYDNJS5-msci-usa-climate-transition-ucits-etf-1d/"/>
-    <x:hyperlink ref="B57:B57" r:id="Rd970e255e82c4fde" display="https://etf.dws.com//en-gb/IE000HT7E0B1-nordic-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B58:B58" r:id="Re0fba449d21d4877" display="https://etf.dws.com//en-gb/IE000HY30YW6-s-p-500-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B59:B59" r:id="R6e4a1ce5d8014077" display="https://etf.dws.com//en-gb/IE000IDLWOL4-s-p-500-equal-weight-scored-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B60:B60" r:id="R3f9c195a22b74f6e" display="https://etf.dws.com//en-gb/IE000INYW0A7-msci-world-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B61:B61" r:id="R929325ed35ef4ecd" display="https://etf.dws.com//en-gb/IE000ISS8DB2-msci-world-small-cap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B62:B62" r:id="Raf8dc678e3e54344" display="https://etf.dws.com//en-gb/IE000JZYIUN0-msci-global-sdg-7-affordable-and-clean-energy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B63:B63" r:id="Rc7c2388bc77344ce" display="https://etf.dws.com//en-gb/IE000KD0BZ68-msci-genomic-healthcare-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B64:B64" r:id="R3e69a3c8a2ea4420" display="https://etf.dws.com//en-gb/IE000L2IS494-msci-global-social-fairness-contributors-ucits-etf-1c/"/>
-    <x:hyperlink ref="B65:B65" r:id="Rc69b3137fdb34917" display="https://etf.dws.com//en-gb/IE000L6ZMMC4-ftse-all-world-ucits-etf-1c/"/>
-    <x:hyperlink ref="B66:B66" r:id="R2924aba6a01b442f" display="https://etf.dws.com//en-gb/IE000LAUZQT6-msci-world-value-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B67:B67" r:id="Rd5ffdb5c2d58406c" display="https://etf.dws.com//en-gb/IE000LOSV2D0-usa-biodiversity-focus-sri-ucits-etf-1c/"/>
-    <x:hyperlink ref="B68:B68" r:id="R4ab54765192f4951" display="https://etf.dws.com//en-gb/IE000M8F3JA6-global-growth-leaders-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B69:B69" r:id="Rd59aeb1f99854971" display="https://etf.dws.com//en-gb/IE000MCVFK47-eur-corporate-green-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B70:B70" r:id="R66393d73793b4a27" display="https://etf.dws.com//en-gb/IE000MF9SZ46-msci-nordic-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B71:B71" r:id="R20d85a2d49c04460" display="https://etf.dws.com//en-gb/IE000N5GJDD7-s-p-500-equal-weight-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B72:B72" r:id="R6bf1a344616d430f" display="https://etf.dws.com//en-gb/IE000N9MLVT1-msci-europe-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B73:B73" r:id="R688090e11cbd41b7" display="https://etf.dws.com//en-gb/IE000NS5HRY9-msci-world-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B74:B74" r:id="Rcf9072ec3af34fae" display="https://etf.dws.com//en-gb/IE000O7Q2E56-electrification-technologies-smart-grid-ucits-etf-1c/"/>
-    <x:hyperlink ref="B75:B75" r:id="R069dfb4090074f62" display="https://etf.dws.com//en-gb/IE000ONQ3X90-msci-world-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B76:B76" r:id="Rb4f2a6f0e1f6430e" display="https://etf.dws.com//en-gb/IE000P4AYI47-msci-world-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B77:B77" r:id="Rd4e447158ce94bb4" display="https://etf.dws.com//en-gb/IE000PDUVTF3-msci-usa-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B78:B78" r:id="R0d22d5436fb04f3e" display="https://etf.dws.com//en-gb/IE000PSF3A70-msci-global-sdgs-ucits-etf-1c/"/>
-    <x:hyperlink ref="B79:B79" r:id="Rc6edad7252a845a2" display="https://etf.dws.com//en-gb/IE000QVYFUT7-india-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B80:B80" r:id="R6002339cad1f4771" display="https://etf.dws.com//en-gb/IE000RNHIKK1-msci-usa-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B81:B81" r:id="R9b6c055b3aaa41d2" display="https://etf.dws.com//en-gb/IE000SRQBBT6-s-p-500-defensive-shareholder-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B82:B82" r:id="Rd9e2cc9b211c4c2d" display="https://etf.dws.com//en-gb/IE000SZ25OI0-s-p-500-equal-weight-scored-screened-ucits-etf-4c-gbp-hedged/"/>
-    <x:hyperlink ref="B83:B83" r:id="R53f630b595614642" display="https://etf.dws.com//en-gb/IE000TL3PL69-msci-world-momentum-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B84:B84" r:id="R82f50954fe0a494c" display="https://etf.dws.com//en-gb/IE000TSML5I8-msci-usa-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B85:B85" r:id="Rabed80f3317b4223" display="https://etf.dws.com//en-gb/IE000TZT8TI0-emerging-markets-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B86:B86" r:id="R855f474fd3844c1e" display="https://etf.dws.com//en-gb/IE000UATQPE2-msci-world-small-cap-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B87:B87" r:id="R46d478f590f84aa9" display="https://etf.dws.com//en-gb/IE000UMV0L21-msci-usa-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B88:B88" r:id="Rc58f749a6bb24741" display="https://etf.dws.com//en-gb/IE000UP2BIZ9-s-p-500-ucits-etf-4d/"/>
-    <x:hyperlink ref="B89:B89" r:id="R577fd1db586b46ad" display="https://etf.dws.com//en-gb/IE000UX5WPU4-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1c/"/>
-    <x:hyperlink ref="B90:B90" r:id="R3b7cfc1120194315" display="https://etf.dws.com//en-gb/IE000UZCJS58-world-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B91:B91" r:id="R9d55d584f8d84ea1" display="https://etf.dws.com//en-gb/IE000V04SL39-msci-usa-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B92:B92" r:id="Raddb79b247f2438e" display="https://etf.dws.com//en-gb/IE000V0GDVU7-msci-global-sdg-11-sustainable-cities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B93:B93" r:id="R952e8220ba5248a9" display="https://etf.dws.com//en-gb/IE000VCBWFL8-msci-emu-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B94:B94" r:id="Rd82dd812aebf4b6a" display="https://etf.dws.com//en-gb/IE000VXC51U5-msci-ac-world-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B95:B95" r:id="Re0b11d762f234736" display="https://etf.dws.com//en-gb/IE000W6L2AI3-msci-emu-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B96:B96" r:id="Rcbffab36b2984004" display="https://etf.dws.com//en-gb/IE000WGF1X01-msci-ac-world-screened-ucits-etf-5c-usd-hedged/"/>
-    <x:hyperlink ref="B97:B97" r:id="R1f77ced7a895426d" display="https://etf.dws.com//en-gb/IE000WHO5BF2-usd-high-yield-corporate-bond-screened-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B98:B98" r:id="R4580332f61464c43" display="https://etf.dws.com//en-gb/IE000WQ16XQ4-msci-europe-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B99:B99" r:id="R72f2565bd8904a2d" display="https://etf.dws.com//en-gb/IE000X1GW0A7-msci-world-imi-ucits-etf-1c/"/>
-    <x:hyperlink ref="B100:B100" r:id="R467ef419efae40aa" display="https://etf.dws.com//en-gb/IE000X4A4GV2-global-equity-top-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B101:B101" r:id="Re672a4fba321428e" display="https://etf.dws.com//en-gb/IE000X5MRP46-msci-usa-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B102:B102" r:id="R22af9e325a7a42ea" display="https://etf.dws.com//en-gb/IE000X63FXN4-usd-corporate-green-bond-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B103:B103" r:id="R1776e02f645245a0" display="https://etf.dws.com//en-gb/IE000X6Z71P5-msci-usa-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B104:B104" r:id="Rbc3e079cd9d049ef" display="https://etf.dws.com//en-gb/IE000XOQ9TK4-msci-next-generation-internet-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B105:B105" r:id="R80442946929e4493" display="https://etf.dws.com//en-gb/IE000Y6L6LE6-emu-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B106:B106" r:id="R0eee866c88604302" display="https://etf.dws.com//en-gb/IE000Y6ZXZ48-msci-global-circular-economy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B107:B107" r:id="R1b8303fe384f45a9" display="https://etf.dws.com//en-gb/IE000YDOORK7-msci-fintech-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B108:B108" r:id="Rc0ff7e371c2f4f54" display="https://etf.dws.com//en-gb/IE000YKHGYN2-ftse-all-world-ex-us-ucits-etf-1c/"/>
-    <x:hyperlink ref="B109:B109" r:id="R97637b1d4fea4fee" display="https://etf.dws.com//en-gb/IE000Z0FC0G5-msci-world-ex-usa-ucits-etf-1d/"/>
-    <x:hyperlink ref="B110:B110" r:id="Ra9827b300ef146a9" display="https://etf.dws.com//en-gb/IE000Z9SJA06-s-p-500-ucits-etf-4c/"/>
-    <x:hyperlink ref="B111:B111" r:id="R8867fa08c18b4d2c" display="https://etf.dws.com//en-gb/IE00B3Y8D011-portfolio-income-ucits-etf-1d/"/>
-    <x:hyperlink ref="B112:B112" r:id="Rf093e5e505fb49ab" display="https://etf.dws.com//en-gb/IE00B8KMSQ34-s-p-500-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B113:B113" r:id="R853949e07af8416d" display="https://etf.dws.com//en-gb/IE00B9MRHC27-msci-nordic-ucits-etf-1d/"/>
-    <x:hyperlink ref="B114:B114" r:id="R4203c64e9fd9420c" display="https://etf.dws.com//en-gb/IE00B9MRJJ36-mdax-esg-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B115:B115" r:id="Re289614ea004495f" display="https://etf.dws.com//en-gb/IE00BCHWNQ94-msci-world-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B116:B116" r:id="Rcb867bbefef54615" display="https://etf.dws.com//en-gb/IE00BCHWNS19-msci-usa-energy-ucits-etf-1d/"/>
-    <x:hyperlink ref="B117:B117" r:id="R9080716780ca42c8" display="https://etf.dws.com//en-gb/IE00BCHWNT26-msci-usa-financials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B118:B118" r:id="R2b85388a87ef47b6" display="https://etf.dws.com//en-gb/IE00BCHWNV48-msci-usa-industrials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B119:B119" r:id="R678986135bb64b8b" display="https://etf.dws.com//en-gb/IE00BCHWNW54-msci-usa-health-care-ucits-etf-1d/"/>
-    <x:hyperlink ref="B120:B120" r:id="R3a7397158e7041ab" display="https://etf.dws.com//en-gb/IE00BD4DX952-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1d/"/>
-    <x:hyperlink ref="B121:B121" r:id="Rf394f50154914ecb" display="https://etf.dws.com//en-gb/IE00BD4DXB77-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B122:B122" r:id="Rebf9bbe8f95344c2" display="https://etf.dws.com//en-gb/IE00BDB7J586-msci-usa-minimum-volatility-ucits-etf-1d/"/>
-    <x:hyperlink ref="B123:B123" r:id="R69893f64975b4032" display="https://etf.dws.com//en-gb/IE00BDGN9Z19-msci-emu-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B124:B124" r:id="Rc3dde5bbb932436d" display="https://etf.dws.com//en-gb/IE00BDR5HM97-usd-high-yield-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B125:B125" r:id="R5ea90a4b76ed4dcf" display="https://etf.dws.com//en-gb/IE00BDR5HN05-usd-high-yield-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B126:B126" r:id="R9ec1adc7da9b4f4f" display="https://etf.dws.com//en-gb/IE00BDVPTJ63-msci-usa-banks-ucits-etf-1d/"/>
-    <x:hyperlink ref="B127:B127" r:id="R35f839e8eaa64aaa" display="https://etf.dws.com//en-gb/IE00BF8J5974-usd-corporate-bond-short-duration-sri-pab-ucits-etf-1d/"/>
-    <x:hyperlink ref="B128:B128" r:id="Rc45a820a971c459d" display="https://etf.dws.com//en-gb/IE00BFMKQ930-usd-corporate-bond-short-duration-sri-pab-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B129:B129" r:id="R0d92961488f6412d" display="https://etf.dws.com//en-gb/IE00BFMKQC67-usd-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B130:B130" r:id="Rd06aea1d18ab441c" display="https://etf.dws.com//en-gb/IE00BFMNHK08-msci-europe-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B131:B131" r:id="R54461e461629472a" display="https://etf.dws.com//en-gb/IE00BFMNPS42-msci-usa-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B132:B132" r:id="R4deda82825404109" display="https://etf.dws.com//en-gb/IE00BG04LT92-usd-high-yield-corporate-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B133:B133" r:id="Ra2e09b26a51e4554" display="https://etf.dws.com//en-gb/IE00BG04LV15-usd-high-yield-corporate-bond-ucits-etf-4d-gbp-hedged/"/>
-    <x:hyperlink ref="B134:B134" r:id="R1b2c40b73331429e" display="https://etf.dws.com//en-gb/IE00BG04LY46-usd-corporate-bond-ucits-etf-5d-gbp-hedged/"/>
-    <x:hyperlink ref="B135:B135" r:id="R3fc4d7a33bc047d9" display="https://etf.dws.com//en-gb/IE00BG04LZ52-msci-usa-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B136:B136" r:id="R781c59e02b774f22" display="https://etf.dws.com//en-gb/IE00BG04M077-msci-usa-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B137:B137" r:id="Raff948f2d31e4d6a" display="https://etf.dws.com//en-gb/IE00BG36TC12-msci-japan-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B138:B138" r:id="R4e57b9351b274e0d" display="https://etf.dws.com//en-gb/IE00BG370F43-msci-emerging-markets-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B139:B139" r:id="Ra1fcb2dc794b4c76" display="https://etf.dws.com//en-gb/IE00BGHQ0G80-msci-ac-world-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B140:B140" r:id="R3cd69df8f9d14729" display="https://etf.dws.com//en-gb/IE00BGJWX091-s-p-500-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B141:B141" r:id="R40d454cb58b847db" display="https://etf.dws.com//en-gb/IE00BGQYRQ28-msci-usa-consumer-staples-ucits-etf-1d/"/>
-    <x:hyperlink ref="B142:B142" r:id="Rfe78f99bd300418d" display="https://etf.dws.com//en-gb/IE00BGQYRR35-msci-usa-consumer-discretionary-ucits-etf-1d/"/>
-    <x:hyperlink ref="B143:B143" r:id="Rddacdc28dc7a4e1d" display="https://etf.dws.com//en-gb/IE00BGQYRS42-msci-usa-information-technology-ucits-etf-1d/"/>
-    <x:hyperlink ref="B144:B144" r:id="R79aa3c9e3e254629" display="https://etf.dws.com//en-gb/IE00BGV5VM45-s-p-europe-ex-uk-ucits-etf-1d/"/>
-    <x:hyperlink ref="B145:B145" r:id="Rfcf958f8372b49b7" display="https://etf.dws.com//en-gb/IE00BGV5VN51-artificial-intelligence-big-data-ucits-etf-1c/"/>
-    <x:hyperlink ref="B146:B146" r:id="Ra81ce4c22a0746f5" display="https://etf.dws.com//en-gb/IE00BGV5VR99-future-mobility-ucits-etf-1c/"/>
-    <x:hyperlink ref="B147:B147" r:id="R33dc957c6fa8478c" display="https://etf.dws.com//en-gb/IE00BH361H73-msci-north-america-high-dividend-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B148:B148" r:id="Rea880b314de24c10" display="https://etf.dws.com//en-gb/IE00BJ0KDQ92-msci-world-ucits-etf-1c/"/>
-    <x:hyperlink ref="B149:B149" r:id="R25e45dd4a9894f80" display="https://etf.dws.com//en-gb/IE00BJ0KDR00-msci-usa-ucits-etf-1c/"/>
-    <x:hyperlink ref="B150:B150" r:id="Rbca871efbd384b05" display="https://etf.dws.com//en-gb/IE00BJZ2DC62-msci-usa-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B151:B151" r:id="Rd2ebf1105a16442a" display="https://etf.dws.com//en-gb/IE00BJZ2DD79-russell-2000-ucits-etf-1c/"/>
-    <x:hyperlink ref="B152:B152" r:id="R932731a1d85f4c8a" display="https://etf.dws.com//en-gb/IE00BK1PV445-msci-usa-ucits-etf-1d/"/>
-    <x:hyperlink ref="B153:B153" r:id="R41ce54e935c5436d" display="https://etf.dws.com//en-gb/IE00BK1PV551-msci-world-ucits-etf-1d/"/>
-    <x:hyperlink ref="B154:B154" r:id="R58fa5fa39d374782" display="https://etf.dws.com//en-gb/IE00BL25JL35-msci-world-quality-ucits-etf-1c/"/>
-    <x:hyperlink ref="B155:B155" r:id="R3de3b8cda5cd4dc0" display="https://etf.dws.com//en-gb/IE00BL25JM42-msci-world-value-ucits-etf-1c/"/>
-    <x:hyperlink ref="B156:B156" r:id="Rf898de324aa748ea" display="https://etf.dws.com//en-gb/IE00BL25JN58-msci-world-minimum-volatility-ucits-etf-1c/"/>
-    <x:hyperlink ref="B157:B157" r:id="R68d632251f354fc2" display="https://etf.dws.com//en-gb/IE00BL25JP72-msci-world-momentum-ucits-etf-1c/"/>
-    <x:hyperlink ref="B158:B158" r:id="Rc40f33e379d24c54" display="https://etf.dws.com//en-gb/IE00BL58LJ19-usd-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B159:B159" r:id="Rc8bd3cd244824008" display="https://etf.dws.com//en-gb/IE00BL58LL31-usd-corporate-bond-sri-pab-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B160:B160" r:id="Rf6a81cf84e5b4463" display="https://etf.dws.com//en-gb/IE00BLNMYC90-s-p-500-equal-weight-ucits-etf-1c/"/>
-    <x:hyperlink ref="B161:B161" r:id="R227aa1e1c1ac47cd" display="https://etf.dws.com//en-gb/IE00BM67HJ62-msci-emerging-markets-ex-china-ucits-etf-1c/"/>
-    <x:hyperlink ref="B162:B162" r:id="Rb5582d1b8dff49df" display="https://etf.dws.com//en-gb/IE00BM67HK77-msci-world-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B163:B163" r:id="R87f6c3bd9ce04be1" display="https://etf.dws.com//en-gb/IE00BM67HL84-msci-world-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B164:B164" r:id="Rf5472b2737d545fa" display="https://etf.dws.com//en-gb/IE00BM67HM91-msci-world-energy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B165:B165" r:id="Rd55f43cfdd524af8" display="https://etf.dws.com//en-gb/IE00BM67HN09-msci-world-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B166:B166" r:id="R4d438f1c14a140f2" display="https://etf.dws.com//en-gb/IE00BM67HP23-msci-world-consumer-discretionary-ucits-etf-1c/"/>
-    <x:hyperlink ref="B167:B167" r:id="R121552caad2144ba" display="https://etf.dws.com//en-gb/IE00BM67HQ30-msci-world-utilities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B168:B168" r:id="Rf69bf06f90fb42a0" display="https://etf.dws.com//en-gb/IE00BM67HR47-msci-world-communication-services-ucits-etf-1c/"/>
-    <x:hyperlink ref="B169:B169" r:id="R03ea71bce4f24455" display="https://etf.dws.com//en-gb/IE00BM67HS53-msci-world-materials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B170:B170" r:id="Rdd3d4418e7154c41" display="https://etf.dws.com//en-gb/IE00BM67HT60-msci-world-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B171:B171" r:id="Ra2656df00cad489b" display="https://etf.dws.com//en-gb/IE00BM67HV82-msci-world-industrials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B172:B172" r:id="R658220ee13444842" display="https://etf.dws.com//en-gb/IE00BM67HW99-s-p-500-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B173:B173" r:id="R30859f90ced242de" display="https://etf.dws.com//en-gb/IE00BM67HX07-s-p-500-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B174:B174" r:id="R025aa8770e8a4a73" display="https://etf.dws.com//en-gb/IE00BM97MR69-us-treasuries-ultrashort-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B175:B175" r:id="R3d6e0b223268464a" display="https://etf.dws.com//en-gb/IE00BM97MV06-us-treasuries-ultrashort-bond-ucits-etf-3c-mxn-hedged/"/>
-    <x:hyperlink ref="B176:B176" r:id="R415a7e95edbe4a2b" display="https://etf.dws.com//en-gb/IE00BMCFJ320-usd-corporate-bond-ucits-etf-6c-mxn-hedged/"/>
-    <x:hyperlink ref="B177:B177" r:id="R4d4c3a16def84679" display="https://etf.dws.com//en-gb/IE00BMFKG444-nasdaq-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B178:B178" r:id="Rf475c3f1ad5649f1" display="https://etf.dws.com//en-gb/IE00BMY76136-msci-world-esg-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B179:B179" r:id="Rcd0b62b9a2014120" display="https://etf.dws.com//en-gb/IE00BN2BCY94-developed-green-real-estate-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B180:B180" r:id="Rad98e6d9c959460c" display="https://etf.dws.com//en-gb/IE00BNC1G699-msci-emu-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B181:B181" r:id="Rcd415b09b1064a76" display="https://etf.dws.com//en-gb/IE00BNC1G707-msci-usa-communication-services-ucits-etf-1d/"/>
-    <x:hyperlink ref="B182:B182" r:id="R5b0ac2f57ec04653" display="https://etf.dws.com//en-gb/IE00BNKF6C99-stoxx-european-market-leaders-ucits-etf-1c/"/>
-    <x:hyperlink ref="B183:B183" r:id="R0055b58f6ce74412" display="https://etf.dws.com//en-gb/IE00BP8FKB21-ftse-developed-europe-ex-uk-real-estate-ucits-etf-1c/"/>
-    <x:hyperlink ref="B184:B184" r:id="Rb7bece0c3c50472d" display="https://etf.dws.com//en-gb/IE00BPVLQD13-msci-japan-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B185:B185" r:id="R16ef37ec85254f13" display="https://etf.dws.com//en-gb/IE00BPVLQF37-msci-japan-screened-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B186:B186" r:id="R5412259fef414edb" display="https://etf.dws.com//en-gb/IE00BQXKVQ19-msci-gcc-select-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B187:B187" r:id="R9ffa1909f26841fc" display="https://etf.dws.com//en-gb/IE00BRB36B93-msci-japan-screened-ucits-etf-3c-eur-hedged/"/>
-    <x:hyperlink ref="B188:B188" r:id="R2b67fde371e441af" display="https://etf.dws.com//en-gb/IE00BTGD1B38-msci-japan-screened-ucits-etf-4c-usd-hedged/"/>
-    <x:hyperlink ref="B189:B189" r:id="R0e7ce7f94ac84354" display="https://etf.dws.com//en-gb/IE00BTJRMP35-msci-emerging-markets-ucits-etf-1c/"/>
-    <x:hyperlink ref="B190:B190" r:id="R2b72d37ea34e4159" display="https://etf.dws.com//en-gb/IE00BYPHT736-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1d/"/>
-    <x:hyperlink ref="B191:B191" r:id="R63edf11bb29f460e" display="https://etf.dws.com//en-gb/IE00BYZNF849-global-infrastructure-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B192:B192" r:id="R20d3a0edbea74dc0" display="https://etf.dws.com//en-gb/IE00BZ02LR44-msci-world-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B193:B193" r:id="Rd2a785550e4c4e4a" display="https://etf.dws.com//en-gb/IE00BZ036H21-usd-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B194:B194" r:id="Rdf3a93390e3c4acc" display="https://etf.dws.com//en-gb/IE00BZ036J45-usd-corporate-bond-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B195:B195" r:id="R62f1bb1289ab44db" display="https://etf.dws.com//en-gb/IE00BZ1BS790-msci-world-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B196:B196" r:id="R0e1fc0700c52462d" display="https://etf.dws.com//en-gb/LU0274208692-msci-world-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B197:B197" r:id="R3d26d031d8ac4688" display="https://etf.dws.com//en-gb/LU0274209237-msci-europe-ucits-etf-1c/"/>
-    <x:hyperlink ref="B198:B198" r:id="Rb7bed0e1b837438a" display="https://etf.dws.com//en-gb/LU0274209740-msci-japan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B199:B199" r:id="R695f4edd19f44518" display="https://etf.dws.com//en-gb/LU0274210672-msci-usa-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B200:B200" r:id="Rc185ed5d18cd4b19" display="https://etf.dws.com//en-gb/LU0274211217-euro-stoxx-50-ucits-etf-1d/"/>
-    <x:hyperlink ref="B201:B201" r:id="Rd216d06c517c4f77" display="https://etf.dws.com//en-gb/LU0274211480-dax-ucits-etf-1c/"/>
-    <x:hyperlink ref="B202:B202" r:id="Ra7d063bde2a34cc5" display="https://etf.dws.com//en-gb/LU0274212538-ftse-mib-ucits-etf-1d/"/>
-    <x:hyperlink ref="B203:B203" r:id="Rb023d8bf855445e9" display="https://etf.dws.com//en-gb/LU0274221281-switzerland-ucits-etf-1d/"/>
-    <x:hyperlink ref="B204:B204" r:id="Re87ad75d3ef0473a" display="https://etf.dws.com//en-gb/LU0290355717-eurozone-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B205:B205" r:id="Re2e3dfd6d67e45d2" display="https://etf.dws.com//en-gb/LU0290356871-eurozone-government-bond-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B206:B206" r:id="Ra1c63a0ec4bb41fe" display="https://etf.dws.com//en-gb/LU0290356954-eurozone-government-bond-3-5-ucits-etf-1c/"/>
-    <x:hyperlink ref="B207:B207" r:id="Rf010f54e6de9401f" display="https://etf.dws.com//en-gb/LU0290357176-eurozone-government-bond-5-7-ucits-etf-1c/"/>
-    <x:hyperlink ref="B208:B208" r:id="R0927fa8289fc4470" display="https://etf.dws.com//en-gb/LU0290357259-eurozone-government-bond-7-10-ucits-etf-1c/"/>
-    <x:hyperlink ref="B209:B209" r:id="Rb04ee029d66143f7" display="https://etf.dws.com//en-gb/LU0290357507-eurozone-government-bond-15-30-ucits-etf-1c/"/>
-    <x:hyperlink ref="B210:B210" r:id="R90f68edf49604beb" display="https://etf.dws.com//en-gb/LU0290357846-eurozone-government-bond-25-ucits-etf-1c/"/>
-    <x:hyperlink ref="B211:B211" r:id="R247465fc5d284038" display="https://etf.dws.com//en-gb/LU0290357929-global-inflation-linked-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B212:B212" r:id="R97160e38bab2446c" display="https://etf.dws.com//en-gb/LU0290358224-eurozone-inflation-linked-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B213:B213" r:id="Rbd04bddd5c1048fc" display="https://etf.dws.com//en-gb/LU0290358497-eur-overnight-rate-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B214:B214" r:id="R5fde6f62403443e9" display="https://etf.dws.com//en-gb/LU0292095535-euro-stoxx-quality-dividend-ucits-etf-1d/"/>
-    <x:hyperlink ref="B215:B215" r:id="R9060bdfe783f433d" display="https://etf.dws.com//en-gb/LU0292096186-stoxx-global-select-dividend-100-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B216:B216" r:id="R0bce22ed950e4fce" display="https://etf.dws.com//en-gb/LU0292097234-ftse-100-income-ucits-etf-1d/"/>
-    <x:hyperlink ref="B217:B217" r:id="R94fa7dfb60b147f8" display="https://etf.dws.com//en-gb/LU0292097317-ftse-250-ucits-etf-1d/"/>
-    <x:hyperlink ref="B218:B218" r:id="Re69eec84051c4044" display="https://etf.dws.com//en-gb/LU0292097747-msci-uk-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B219:B219" r:id="R7168dfa7606d454b" display="https://etf.dws.com//en-gb/LU0292100046-msci-korea-ucits-etf-1c/"/>
-    <x:hyperlink ref="B220:B220" r:id="R532fda8a3ff04048" display="https://etf.dws.com//en-gb/LU0292100806-msci-europe-materials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B221:B221" r:id="R7f0c8778bf6740ae" display="https://etf.dws.com//en-gb/LU0292103222-msci-europe-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B222:B222" r:id="Rd2313ed1ba2b4516" display="https://etf.dws.com//en-gb/LU0292103651-msci-europe-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B223:B223" r:id="R46e5bb49807b409f" display="https://etf.dws.com//en-gb/LU0292104030-msci-europe-communication-services-ucits-etf-1c/"/>
-    <x:hyperlink ref="B224:B224" r:id="R5894cf22ec534150" display="https://etf.dws.com//en-gb/LU0292104469-msci-europe-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B225:B225" r:id="R1c27f6b92dbe43cc" display="https://etf.dws.com//en-gb/LU0292104899-msci-europe-utilities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B226:B226" r:id="Re055cd1049e244db" display="https://etf.dws.com//en-gb/LU0292105359-msci-europe-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B227:B227" r:id="R1a5811bc7e174f3f" display="https://etf.dws.com//en-gb/LU0292106084-msci-europe-industrials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B228:B228" r:id="R0ea3eb0e988b424b" display="https://etf.dws.com//en-gb/LU0292106167-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B229:B229" r:id="Rdd800c540db941df" display="https://etf.dws.com//en-gb/LU0292106241-shortdax-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B230:B230" r:id="R72116eb776ef48d2" display="https://etf.dws.com//en-gb/LU0292106753-euro-stoxx-50-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B231:B231" r:id="R710b806dc76d43c2" display="https://etf.dws.com//en-gb/LU0292107645-msci-emerging-markets-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B232:B232" r:id="R8427eaca159340d9" display="https://etf.dws.com//en-gb/LU0292107991-msci-em-asia-screened-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B233:B233" r:id="R7ad0a8a6c4ae4778" display="https://etf.dws.com//en-gb/LU0292108619-msci-em-latin-america-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B234:B234" r:id="Ra11f6b223c1740a9" display="https://etf.dws.com//en-gb/LU0292109005-msci-em-europe-middle-east-africa-esg-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B235:B235" r:id="R4cb5d81ee6514129" display="https://etf.dws.com//en-gb/LU0292109187-msci-taiwan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B236:B236" r:id="R5027612113c94ab7" display="https://etf.dws.com//en-gb/LU0292109344-msci-brazil-ucits-etf-1c/"/>
-    <x:hyperlink ref="B237:B237" r:id="R85119e1e475546ff" display="https://etf.dws.com//en-gb/LU0292109690-nifty-50-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B238:B238" r:id="R6a78928fdf0a4b07" display="https://etf.dws.com//en-gb/LU0292109856-msci-china-a-ucits-etf-1c/"/>
-    <x:hyperlink ref="B239:B239" r:id="R71f46b883ed842a3" display="https://etf.dws.com//en-gb/LU0321462870-itraxx-crossover-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B240:B240" r:id="Re1d4929b31ea43ae" display="https://etf.dws.com//en-gb/LU0321462953-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B241:B241" r:id="R5fb16963185549cf" display="https://etf.dws.com//en-gb/LU0321464652-gbp-overnight-rate-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B242:B242" r:id="Rcebf09386c9b45d1" display="https://etf.dws.com//en-gb/LU0321465469-usd-overnight-rate-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B243:B243" r:id="Rb323df99e6b2415c" display="https://etf.dws.com//en-gb/LU0322248146-sli-ucits-etf-1d/"/>
-    <x:hyperlink ref="B244:B244" r:id="Rd12a00ea91964baa" display="https://etf.dws.com//en-gb/LU0322250712-lpx-private-equity-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B245:B245" r:id="R3a927c6360164d13" display="https://etf.dws.com//en-gb/LU0322250985-cac-40-ucits-etf-1d/"/>
-    <x:hyperlink ref="B246:B246" r:id="R602c05f14d4244f6" display="https://etf.dws.com//en-gb/LU0322251520-s-p-500-inverse-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B247:B247" r:id="R099a3b394287404c" display="https://etf.dws.com//en-gb/LU0322252171-msci-ac-asia-ex-japan-esg-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B248:B248" r:id="R0756a9eed2624a6b" display="https://etf.dws.com//en-gb/LU0322252338-msci-pacific-ex-japan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B249:B249" r:id="R00f4ad5924d346be" display="https://etf.dws.com//en-gb/LU0322252924-vietnam-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B250:B250" r:id="R822f6d5f885f4b72" display="https://etf.dws.com//en-gb/LU0322253229-s-p-global-infrastructure-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B251:B251" r:id="Ra461de2d7b58456a" display="https://etf.dws.com//en-gb/LU0322253732-msci-europe-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B252:B252" r:id="Rfc776344c52340b6" display="https://etf.dws.com//en-gb/LU0322253906-msci-europe-small-cap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B253:B253" r:id="R7b00249acf424e9a" display="https://etf.dws.com//en-gb/LU0328473581-ftse-100-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B254:B254" r:id="Rdddddb409c304708" display="https://etf.dws.com//en-gb/LU0328474803-s-p-asx-200-ucits-etf-1d/"/>
-    <x:hyperlink ref="B255:B255" r:id="R67e14ad4cce04fa5" display="https://etf.dws.com//en-gb/LU0328475792-stoxx-europe-600-ucits-etf-1c/"/>
-    <x:hyperlink ref="B256:B256" r:id="R7c2788e984044d39" display="https://etf.dws.com//en-gb/LU0328476410-s-p-select-frontier-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B257:B257" r:id="R85b86e585f8d43f2" display="https://etf.dws.com//en-gb/LU0335044896-eur-overnight-rate-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B258:B258" r:id="Rcfe5e4aa36ab4c03" display="https://etf.dws.com//en-gb/LU0378818131-global-government-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B259:B259" r:id="Rc7c9910766ca4c42" display="https://etf.dws.com//en-gb/LU0378818560-singapore-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B260:B260" r:id="R4d6c63b1b15848fb" display="https://etf.dws.com//en-gb/LU0380865021-euro-stoxx-50-ucits-etf-1c/"/>
-    <x:hyperlink ref="B261:B261" r:id="Rbd6a13ba6d1f4f37" display="https://etf.dws.com//en-gb/LU0397221945-portfolio-ucits-etf-1c/"/>
-    <x:hyperlink ref="B262:B262" r:id="R99f5f11450a3451d" display="https://etf.dws.com//en-gb/LU0411075020-shortdax-x2-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B263:B263" r:id="Rd30454cd4ce64a0d" display="https://etf.dws.com//en-gb/LU0411075376-levdax-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B264:B264" r:id="Rbf268727377e4093" display="https://etf.dws.com//en-gb/LU0411078552-s-p-500-2x-leveraged-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B265:B265" r:id="Ra634071e623f403c" display="https://etf.dws.com//en-gb/LU0411078636-s-p-500-2x-inverse-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B266:B266" r:id="Rd950dad8cd0f4cd2" display="https://etf.dws.com//en-gb/LU0429458895-us-treasuries-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B267:B267" r:id="R12a7a4803f4e419a" display="https://etf.dws.com//en-gb/LU0429459356-us-treasuries-ucits-etf-1d/"/>
-    <x:hyperlink ref="B268:B268" r:id="R8870021dc3474583" display="https://etf.dws.com//en-gb/LU0429790743-bloomberg-commodity-swap-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B269:B269" r:id="Rafafb2bebfd24f9a" display="https://etf.dws.com//en-gb/LU0460391732-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-2c/"/>
-    <x:hyperlink ref="B270:B270" r:id="R3c9192982b044422" display="https://etf.dws.com//en-gb/LU0460391906-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-3c-gbp-hedged/"/>
-    <x:hyperlink ref="B271:B271" r:id="Rb9d7585df9a94ce1" display="https://etf.dws.com//en-gb/LU0468896575-germany-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B272:B272" r:id="R58900ef597234970" display="https://etf.dws.com//en-gb/LU0468897110-germany-government-bond-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B273:B273" r:id="R4e55d9fb490a41b1" display="https://etf.dws.com//en-gb/LU0476289466-msci-mexico-ucits-etf-1c/"/>
-    <x:hyperlink ref="B274:B274" r:id="R6495a2702cf74050" display="https://etf.dws.com//en-gb/LU0476289540-msci-canada-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B275:B275" r:id="R0d04ac5c5d774340" display="https://etf.dws.com//en-gb/LU0476289623-msci-indonesia-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B276:B276" r:id="R1133bc90021f4169" display="https://etf.dws.com//en-gb/LU0478205379-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B277:B277" r:id="R5976580befd84909" display="https://etf.dws.com//en-gb/LU0478205965-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B278:B278" r:id="Rdd1e5cf6219d4f95" display="https://etf.dws.com//en-gb/LU0484968812-eur-corporate-bond-sri-pab-ucits-etf-1d/"/>
-    <x:hyperlink ref="B279:B279" r:id="Rbdca9086b15d4316" display="https://etf.dws.com//en-gb/LU0484968903-eur-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B280:B280" r:id="Rf37d7c0af807470c" display="https://etf.dws.com//en-gb/LU0484969463-target-maturity-sept-2029-italy-and-spain-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B281:B281" r:id="R89f92d9cf7794fd8" display="https://etf.dws.com//en-gb/LU0486851024-msci-europe-value-ucits-etf-1c/"/>
-    <x:hyperlink ref="B282:B282" r:id="R0130e306f4324f2f" display="https://etf.dws.com//en-gb/LU0489337690-ftse-developed-europe-real-estate-ucits-etf-1c/"/>
-    <x:hyperlink ref="B283:B283" r:id="Rfa7dc46751444bc4" display="https://etf.dws.com//en-gb/LU0490618542-s-p-500-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B284:B284" r:id="Ra1f35d848d8c43b5" display="https://etf.dws.com//en-gb/LU0494592974-australia-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B285:B285" r:id="R56dc8d7504004c50" display="https://etf.dws.com//en-gb/LU0514694370-msci-malaysia-ucits-etf-1c/"/>
-    <x:hyperlink ref="B286:B286" r:id="R37cb5420d7f14cb3" display="https://etf.dws.com//en-gb/LU0514694701-msci-thailand-ucits-etf-1c/"/>
-    <x:hyperlink ref="B287:B287" r:id="R62ae2bf7fec7460e" display="https://etf.dws.com//en-gb/LU0514695187-msci-india-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B288:B288" r:id="R880b05e7fa914bdc" display="https://etf.dws.com//en-gb/LU0514695690-msci-china-ucits-etf-1c/"/>
-    <x:hyperlink ref="B289:B289" r:id="R803d5541c63846de" display="https://etf.dws.com//en-gb/LU0524480265-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1c/"/>
-    <x:hyperlink ref="B290:B290" r:id="Rb607d4880683493c" display="https://etf.dws.com//en-gb/LU0592215403-msci-philippines-ucits-etf-1c/"/>
-    <x:hyperlink ref="B291:B291" r:id="Rf733519cd4d94827" display="https://etf.dws.com//en-gb/LU0592216393-spain-ucits-etf-1c/"/>
-    <x:hyperlink ref="B292:B292" r:id="R5a7115ab17c64170" display="https://etf.dws.com//en-gb/LU0592217524-msci-africa-top-50-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B293:B293" r:id="R6092560753c04845" display="https://etf.dws.com//en-gb/LU0613540268-italy-government-bond-0-1-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B294:B294" r:id="R3c96a161c0b346d9" display="https://etf.dws.com//en-gb/LU0614173549-eurozone-government-bond-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B295:B295" r:id="R4536906d07984a83" display="https://etf.dws.com//en-gb/LU0614173895-eurozone-government-bond-3-5-ucits-etf-1d/"/>
-    <x:hyperlink ref="B296:B296" r:id="R15d501be9dd34470" display="https://etf.dws.com//en-gb/LU0641006290-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B297:B297" r:id="R0bd360f81965463e" display="https://etf.dws.com//en-gb/LU0641006456-global-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B298:B298" r:id="R9ddb8c954a4641af" display="https://etf.dws.com//en-gb/LU0641006613-global-government-bond-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B299:B299" r:id="R4d9ef86dea8347dc" display="https://etf.dws.com//en-gb/LU0641007009-global-inflation-linked-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B300:B300" r:id="R5116f23cf6d74ee1" display="https://etf.dws.com//en-gb/LU0641007264-global-inflation-linked-bond-ucits-etf-3d-gbp-hedged/"/>
-    <x:hyperlink ref="B301:B301" r:id="R860032b9aed445ff" display="https://etf.dws.com//en-gb/LU0641007421-global-inflation-linked-bond-ucits-etf-4d-chf-hedged/"/>
-    <x:hyperlink ref="B302:B302" r:id="Rd0abc26965f14e0d" display="https://etf.dws.com//en-gb/LU0643975161-germany-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B303:B303" r:id="Rb9996ffcef724f5f" display="https://etf.dws.com//en-gb/LU0643975591-eurozone-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B304:B304" r:id="R949bafc261484088" display="https://etf.dws.com//en-gb/LU0659578842-msci-singapore-ucits-etf-1c/"/>
-    <x:hyperlink ref="B305:B305" r:id="Re86447d1ba434f1d" display="https://etf.dws.com//en-gb/LU0659579063-atx-ucits-etf-1c/"/>
-    <x:hyperlink ref="B306:B306" r:id="R22029ffe60fe4f5a" display="https://etf.dws.com//en-gb/LU0659579147-msci-pakistan-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B307:B307" r:id="Ra5f952b8c19f433e" display="https://etf.dws.com//en-gb/LU0659579733-msci-world-swap-ucits-etf-4c-eur-hedged/"/>
-    <x:hyperlink ref="B308:B308" r:id="R36308250e43043c4" display="https://etf.dws.com//en-gb/LU0659580079-msci-japan-ucits-etf-4c-eur-hedged/"/>
-    <x:hyperlink ref="B309:B309" r:id="R58c604d8a1e04e09" display="https://etf.dws.com//en-gb/LU0677077884-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2d/"/>
-    <x:hyperlink ref="B310:B310" r:id="Rc36e3680a14d4f0b" display="https://etf.dws.com//en-gb/LU0690964092-global-government-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B311:B311" r:id="R84cbdb701c1d46a4" display="https://etf.dws.com//en-gb/LU0779800910-csi300-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B312:B312" r:id="R5b64b6bd1c20477f" display="https://etf.dws.com//en-gb/LU0838780707-ftse-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B313:B313" r:id="R5a6086cbf8ba4a1e" display="https://etf.dws.com//en-gb/LU0838782315-dax-esg-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B314:B314" r:id="R3e223482ef2543c6" display="https://etf.dws.com//en-gb/LU0839027447-nikkei-225-ucits-etf-1d/"/>
-    <x:hyperlink ref="B315:B315" r:id="R7323c2ea08c3466a" display="https://etf.dws.com//en-gb/LU0846194776-msci-emu-ucits-etf-1d/"/>
-    <x:hyperlink ref="B316:B316" r:id="R2754995d45b74e13" display="https://etf.dws.com//en-gb/LU0875160326-harvest-csi300-ucits-etf-1d/"/>
-    <x:hyperlink ref="B317:B317" r:id="Rd31c7c95b0424a43" display="https://etf.dws.com//en-gb/LU0908508731-global-government-bond-ucits-etf-5c/"/>
-    <x:hyperlink ref="B318:B318" r:id="R9dfa92d8c48a4b71" display="https://etf.dws.com//en-gb/LU0908508814-global-inflation-linked-bond-ucits-etf-5c/"/>
-    <x:hyperlink ref="B319:B319" r:id="R09f7603493a54ac5" display="https://etf.dws.com//en-gb/LU0925589839-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B320:B320" r:id="Rfbbcd361e15d414a" display="https://etf.dws.com//en-gb/LU0927735406-msci-japan-ucits-etf-2d-usd-hedged/"/>
-    <x:hyperlink ref="B321:B321" r:id="Rcb1166af28bb4fd7" display="https://etf.dws.com//en-gb/LU0942970103-esg-global-aggregate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B322:B322" r:id="R023b92e0a6d44b29" display="https://etf.dws.com//en-gb/LU0942970285-esg-global-aggregate-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B323:B323" r:id="R4199837b54364f96" display="https://etf.dws.com//en-gb/LU0942970368-esg-global-aggregate-bond-ucits-etf-3d-gbp-hedged/"/>
-    <x:hyperlink ref="B324:B324" r:id="R45e89066a58a42e4" display="https://etf.dws.com//en-gb/LU0942970442-esg-global-aggregate-bond-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B325:B325" r:id="R6c73eb44d4de4edd" display="https://etf.dws.com//en-gb/LU0942970798-esg-global-aggregate-bond-ucits-etf-5c-eur-hedged/"/>
-    <x:hyperlink ref="B326:B326" r:id="Ra7ad38a042b54d1f" display="https://etf.dws.com//en-gb/LU0943504760-switzerland-ucits-etf-1c/"/>
-    <x:hyperlink ref="B327:B327" r:id="R16d11674cd45428c" display="https://etf.dws.com//en-gb/LU0952581584-japan-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B328:B328" r:id="Re23280f2cfc2443f" display="https://etf.dws.com//en-gb/LU0962071741-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1d/"/>
-    <x:hyperlink ref="B329:B329" r:id="Rd2494409274f4858" display="https://etf.dws.com//en-gb/LU0962078753-global-inflation-linked-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B330:B330" r:id="Rc79caf944cc14208" display="https://etf.dws.com//en-gb/LU0994505336-spain-ucits-etf-1d/"/>
-    <x:hyperlink ref="B331:B331" r:id="R4ec268abf8e5458a" display="https://etf.dws.com//en-gb/LU1094612022-harvest-china-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B332:B332" r:id="Rdc6457fd2ae04483" display="https://etf.dws.com//en-gb/LU1109939865-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1d/"/>
-    <x:hyperlink ref="B333:B333" r:id="Recccd715a244497e" display="https://etf.dws.com//en-gb/LU1109941689-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B334:B334" r:id="R7c839455da334b37" display="https://etf.dws.com//en-gb/LU1109942653-eur-high-yield-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B335:B335" r:id="R0776e6ef786f483d" display="https://etf.dws.com//en-gb/LU1109943388-eur-high-yield-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B336:B336" r:id="Rfd84bc5613a8471d" display="https://etf.dws.com//en-gb/LU1127514245-msci-emu-ucits-etf-1c-usd-hedged/"/>
-    <x:hyperlink ref="B337:B337" r:id="R79b1652c3db64685" display="https://etf.dws.com//en-gb/LU1127516455-msci-emu-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B338:B338" r:id="R1ea358dc0975406e" display="https://etf.dws.com//en-gb/LU1184092051-msci-europe-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B339:B339" r:id="Rabc62ef29e184fd4" display="https://etf.dws.com//en-gb/LU1215827756-msci-japan-ucits-etf-7c-chf-hedged/"/>
-    <x:hyperlink ref="B340:B340" r:id="R0ef464f6f2804b93" display="https://etf.dws.com//en-gb/LU1215828218-msci-emu-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B341:B341" r:id="R583df14d6ec64e55" display="https://etf.dws.com//en-gb/LU1221100792-dax-esg-screened-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B342:B342" r:id="R5ff4b9fd8cf54fc5" display="https://etf.dws.com//en-gb/LU1221102491-dax-esg-screened-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B343:B343" r:id="R238812678a274d26" display="https://etf.dws.com//en-gb/LU1242369327-msci-europe-ucits-etf-1d/"/>
-    <x:hyperlink ref="B344:B344" r:id="R4b2f574771194c00" display="https://etf.dws.com//en-gb/LU1310477036-harvest-csi-a500-ucits-etf-1d/"/>
-    <x:hyperlink ref="B345:B345" r:id="Racca51a8891c4585" display="https://etf.dws.com//en-gb/LU1349386927-dax-ucits-etf-1d/"/>
-    <x:hyperlink ref="B346:B346" r:id="Red38db08162048fe" display="https://etf.dws.com//en-gb/LU1399300455-us-treasuries-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B347:B347" r:id="R8ecc2c11fa29402d" display="https://etf.dws.com//en-gb/LU1772333404-stoxx-europe-600-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B348:B348" r:id="R1485b146afcf4687" display="https://etf.dws.com//en-gb/LU1875395870-nikkei-225-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B349:B349" r:id="R9f85cb2e05f841f0" display="https://etf.dws.com//en-gb/LU1920015440-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2c/"/>
-    <x:hyperlink ref="B350:B350" r:id="R89b37d68c0f74b6b" display="https://etf.dws.com//en-gb/LU1920015523-us-treasuries-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B351:B351" r:id="R259adfd86a7c4902" display="https://etf.dws.com//en-gb/LU1920015796-us-treasuries-ucits-etf-1c/"/>
-    <x:hyperlink ref="B352:B352" r:id="Ra24dcff619ff4498" display="https://etf.dws.com//en-gb/LU2009147591-eurozone-government-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B353:B353" r:id="Rf723e9327c764c44" display="https://etf.dws.com//en-gb/LU2009147757-s-p-500-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B354:B354" r:id="Rbd69bed316c24f5a" display="https://etf.dws.com//en-gb/LU2158769930-j-p-morgan-em-local-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B355:B355" r:id="Rd92c17bf01d040d4" display="https://etf.dws.com//en-gb/LU2178481649-eur-corporate-bond-short-duration-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B356:B356" r:id="R270dbb7c0d70497e" display="https://etf.dws.com//en-gb/LU2196470426-nikkei-225-ucits-etf-1c/"/>
-    <x:hyperlink ref="B357:B357" r:id="R4b988c35553743ac" display="https://etf.dws.com//en-gb/LU2196472984-s-p-500-swap-ucits-etf-5c-eur-hedged/"/>
-    <x:hyperlink ref="B358:B358" r:id="R5870b96186b346fa" display="https://etf.dws.com//en-gb/LU2196473016-s-p-500-swap-ucits-etf-7c-gbp-hedged/"/>
-    <x:hyperlink ref="B359:B359" r:id="R5e2bd530cdce4114" display="https://etf.dws.com//en-gb/LU2263803533-msci-world-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B360:B360" r:id="R14f11b28f2a84d6a" display="https://etf.dws.com//en-gb/LU2278080713-bloomberg-commodity-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B361:B361" r:id="R3d3eebcf5e214bfa" display="https://etf.dws.com//en-gb/LU2296661775-msci-em-asia-screened-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B362:B362" r:id="R13508fa5f9d64641" display="https://etf.dws.com//en-gb/LU2361257269-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B363:B363" r:id="R45c62ad822244cdb" display="https://etf.dws.com//en-gb/LU2376679564-harvest-msci-china-tech-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B364:B364" r:id="R916bc29790b7489c" display="https://etf.dws.com//en-gb/LU2385068163-esg-global-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B365:B365" r:id="R55df85bdd9e048d0" display="https://etf.dws.com//en-gb/LU2385068247-esg-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B366:B366" r:id="R57253af264ac457b" display="https://etf.dws.com//en-gb/LU2385068320-esg-global-government-bond-ucits-etf-3d-usd-hedged/"/>
-    <x:hyperlink ref="B367:B367" r:id="Ra423441658ad4a9e" display="https://etf.dws.com//en-gb/LU2385068593-esg-global-government-bond-ucits-etf-4d-eur-hedged/"/>
-    <x:hyperlink ref="B368:B368" r:id="Rb1107a135c194e5d" display="https://etf.dws.com//en-gb/LU2456436083-msci-china-ucits-etf-1d/"/>
-    <x:hyperlink ref="B369:B369" r:id="Rf99a9ae788074983" display="https://etf.dws.com//en-gb/LU2462217071-esg-global-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B370:B370" r:id="R658be75735ad46e0" display="https://etf.dws.com//en-gb/LU2468423459-esg-eurozone-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B371:B371" r:id="Ree4d0e3823914764" display="https://etf.dws.com//en-gb/LU2469465822-msci-china-a-screened-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B372:B372" r:id="Rf929c1fa90744060" display="https://etf.dws.com//en-gb/LU2504532131-tips-us-inflation-linked-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B373:B373" r:id="R05351e922fa74585" display="https://etf.dws.com//en-gb/LU2504532487-eurozone-government-green-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B374:B374" r:id="Rddf8cfcb1b5149d5" display="https://etf.dws.com//en-gb/LU2504537445-eurozone-government-bond-esg-tilted-ucits-etf-1d/"/>
-    <x:hyperlink ref="B375:B375" r:id="R8f7d35af3e3b447e" display="https://etf.dws.com//en-gb/LU2523865728-eurozone-government-bond-7-10-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B376:B376" r:id="Re2411a9d9f89466f" display="https://etf.dws.com//en-gb/LU2523865991-eurozone-government-bond-7-10-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B377:B377" r:id="R94050a891e39417f" display="https://etf.dws.com//en-gb/LU2523866023-eurozone-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B378:B378" r:id="Rd2b5fa1423c5463c" display="https://etf.dws.com//en-gb/LU2523866296-germany-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B379:B379" r:id="Rf181002ca3704a92" display="https://etf.dws.com//en-gb/LU2523866379-germany-government-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B380:B380" r:id="R4642bfa37c454485" display="https://etf.dws.com//en-gb/LU2552296563-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-2d/"/>
-    <x:hyperlink ref="B381:B381" r:id="R79814bcc0fc343b0" display="https://etf.dws.com//en-gb/LU2581375073-msci-usa-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B382:B382" r:id="R72c08abbf6274f4a" display="https://etf.dws.com//en-gb/LU2581375156-stoxx-europe-600-ucits-etf-1d/"/>
-    <x:hyperlink ref="B383:B383" r:id="Ra5960fd90b2e486b" display="https://etf.dws.com//en-gb/LU2581375230-msci-japan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B384:B384" r:id="Rb19b7343a25042c7" display="https://etf.dws.com//en-gb/LU2606231335-eurozone-government-bond-3-5-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B385:B385" r:id="R5049d3851b0f4eac" display="https://etf.dws.com//en-gb/LU2606231418-eurozone-government-bond-3-5-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B386:B386" r:id="R735de89ee0aa45da" display="https://etf.dws.com//en-gb/LU2610432036-us-treasuries-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B387:B387" r:id="R775bffaeee6b4c82" display="https://etf.dws.com//en-gb/LU2641054122-eurozone-government-bond-0-1-ucits-etf-1c/"/>
-    <x:hyperlink ref="B388:B388" r:id="R9ddaba4a1f2f4aab" display="https://etf.dws.com//en-gb/LU2641054551-germany-government-bond-0-1-ucits-etf-1c/"/>
-    <x:hyperlink ref="B389:B389" r:id="Rf28b8b2aed39493a" display="https://etf.dws.com//en-gb/LU2662649412-us-treasuries-10-ucits-etf-1d/"/>
-    <x:hyperlink ref="B390:B390" r:id="R3fbf5114013f4232" display="https://etf.dws.com//en-gb/LU2662649503-us-treasuries-3-7-ucits-etf-1d/"/>
-    <x:hyperlink ref="B391:B391" r:id="Rbb16718aa80c4858" display="https://etf.dws.com//en-gb/LU2662649685-us-treasuries-7-10-ucits-etf-1d/"/>
-    <x:hyperlink ref="B392:B392" r:id="R6186fe98382c4db3" display="https://etf.dws.com//en-gb/LU2673522830-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B393:B393" r:id="R7274e7ff02884ace" display="https://etf.dws.com//en-gb/LU2673522913-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B394:B394" r:id="R79b7671ca7e24917" display="https://etf.dws.com//en-gb/LU2673523051-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B395:B395" r:id="R35eadd62329d4c46" display="https://etf.dws.com//en-gb/LU2673523135-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B396:B396" r:id="Rd1ed313e7d144ad2" display="https://etf.dws.com//en-gb/LU2673523218-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B397:B397" r:id="Rb3dfb9c7af1c4dd9" display="https://etf.dws.com//en-gb/LU2673523309-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B398:B398" r:id="Ra66a1f990d114c84" display="https://etf.dws.com//en-gb/LU2673523481-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B399:B399" r:id="R0ed264efb85943f3" display="https://etf.dws.com//en-gb/LU2673523564-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B400:B400" r:id="Rab050175df4543a7" display="https://etf.dws.com//en-gb/LU2675291913-msci-emerging-markets-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B401:B401" r:id="R61de9bc2c73e4fd2" display="https://etf.dws.com//en-gb/LU2755521270-msci-pacific-ex-japan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B402:B402" r:id="Rb5f2427b2e404b10" display="https://etf.dws.com//en-gb/LU2788421340-csi500-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B403:B403" r:id="R700ab8d94c2e490a" display="https://etf.dws.com//en-gb/LU2809864296-target-maturity-sept-2030-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B404:B404" r:id="Rcbb6687c7f9b4d56" display="https://etf.dws.com//en-gb/LU2809864452-target-maturity-sept-2032-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B405:B405" r:id="Rf15f3c3b8c1945db" display="https://etf.dws.com//en-gb/LU2809864619-target-maturity-sept-2034-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B406:B406" r:id="R050c94ad9d084026" display="https://etf.dws.com//en-gb/LU2810185665-target-maturity-sept-2028-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B407:B407" r:id="Rf869af85c3d34dd7" display="https://etf.dws.com//en-gb/LU2859297330-world-small-cap-green-tech-innovators-ucits-etf-1c/"/>
-    <x:hyperlink ref="B408:B408" r:id="Rd2fd5c010d954446" display="https://etf.dws.com//en-gb/LU2859392081-world-green-tech-innovators-ucits-etf-1c/"/>
-    <x:hyperlink ref="B409:B409" r:id="Rec28e9ce0e244bdf" display="https://etf.dws.com//en-gb/LU2903252349-scalable-msci-ac-world-xtrackers-ucits-etf-1c/"/>
-    <x:hyperlink ref="B410:B410" r:id="Re01a58c5cd444797" display="https://etf.dws.com//en-gb/LU2928641757-msci-taiwan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B411:B411" r:id="Ra3a10e9e63ea475e" display="https://etf.dws.com//en-gb/LU3003217554-eurozone-government-bond-1-3-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B412:B412" r:id="R1b693e51664f4a2a" display="https://etf.dws.com//en-gb/LU3003217638-eurozone-government-bond-1-3-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B413:B413" r:id="Rad4ce03ef6d54923" display="https://etf.dws.com//en-gb/LU3003217711-eurozone-government-bond-5-7-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B414:B414" r:id="R5a22b5b00b2a4bf4" display="https://etf.dws.com//en-gb/LU3003217984-eurozone-government-bond-5-7-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B415:B415" r:id="Rd225764b57244f3a" display="https://etf.dws.com//en-gb/LU3003218016-australia-government-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B416:B416" r:id="R38a0663cb97e4bac" display="https://etf.dws.com//en-gb/LU3003218107-australia-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B417:B417" r:id="Rb7d6805f70254145" display="https://etf.dws.com//en-gb/LU3003218362-australia-government-bond-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B418:B418" r:id="R73912dc49ff34563" display="https://etf.dws.com//en-gb/LU3003218446-japan-government-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B419:B419" r:id="Rca51857da84b4ca6" display="https://etf.dws.com//en-gb/LU3003218792-japan-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B420:B420" r:id="R6186b994190a48d0" display="https://etf.dws.com//en-gb/LU3003218958-japan-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B421:B421" r:id="R8c88ac34110e424b" display="https://etf.dws.com//en-gb/LU3061478973-europe-defence-technologies-ucits-etf-1c/"/>
-    <x:hyperlink ref="B422:B422" r:id="R43dfcdeabfc44edb" display="https://etf.dws.com//en-gb/LU3116008346-diversified-portfolio-20-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B423:B423" r:id="Rce4822365f404c63" display="https://etf.dws.com//en-gb/LU3116008429-diversified-portfolio-40-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B424:B424" r:id="Rc891bd6491ab42af" display="https://etf.dws.com//en-gb/LU3116008692-diversified-portfolio-60-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B425:B425" r:id="R0256f7b26c8d469f" display="https://etf.dws.com//en-gb/LU3116008775-diversified-portfolio-80-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B426:B426" r:id="R47848e4833984abd" display="https://etf.dws.com//en-gb/LU3121019551-global-government-bond-ucits-etf-3d-chf-hedged/"/>
-    <x:hyperlink ref="B427:B427" r:id="R8dadb90bce0d4382" display="https://etf.dws.com//en-gb/LU3123443510-salam-usd-global-aggregate-sukuk-ucits-etf-1d/"/>
-    <x:hyperlink ref="B428:B428" r:id="R24956b1be29b4b20" display="https://etf.dws.com//en-gb/LU3184977026-msci-world-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B429:B429" r:id="R26a728a176224b6e" display="https://etf.dws.com//en-gb/LU3184977299-msci-europe-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B430:B430" r:id="R88e42d6e53d9476c" display="https://etf.dws.com//en-gb/LU3184977372-msci-usa-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B431:B431" r:id="Rdea48d732f70444f" display="https://etf.dws.com//en-gb/LU3184977455-msci-emerging-markets-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B432:B432" r:id="R14a8a6ac62bf41c7" display="https://etf.dws.com//en-gb/LU3184977612-s-p-500-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B433:B433" r:id="Rcb9d5797403a42c0" display="https://etf.dws.com//en-gb/LU3184977703-ftse-100-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B434:B434" r:id="R538c6f7565ea438e" display="https://etf.dws.com//en-gb/LU3198621024-s-p-500-swap-ucits-etf-ic-usd-unlisted/"/>
-    <x:hyperlink ref="B435:B435" r:id="R907f5311b95340bf" display="https://etf.dws.com//en-gb/LU3284391318-global-government-bond-ucits-etf-4d/"/>
-    <x:hyperlink ref="B436:B436" r:id="R6bd08b31d9e64b2a" display="https://etf.dws.com//en-gb/LU3353962940-stoxx-europe-600-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B8:B8" r:id="R9f7034e2b64a48fd" display="https://etf.dws.com//en-gb/IE00002ZKAP0-europe-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B9:B9" r:id="R2473fcef61584466" display="https://etf.dws.com//en-gb/IE00004DJ199-msci-world-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B10:B10" r:id="R20c521bc456b4fc9" display="https://etf.dws.com//en-gb/IE0000K7HU41-msci-usa-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B11:B11" r:id="R5183f8f4cd68486c" display="https://etf.dws.com//en-gb/IE0000MMQ5M5-msci-usa-esg-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B12:B12" r:id="R6a5667c70b7f47e3" display="https://etf.dws.com//en-gb/IE0001JH5CB4-europe-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B13:B13" r:id="Reca57de44e1e49d8" display="https://etf.dws.com//en-gb/IE0001TLQX55-s-p-500-garp-ucits-etf-1c/"/>
+    <x:hyperlink ref="B14:B14" r:id="R170ec6c969e3459d" display="https://etf.dws.com//en-gb/IE00028H9QJ8-usd-corporate-green-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B15:B15" r:id="Rb80eb8e333a84df3" display="https://etf.dws.com//en-gb/IE0002EI5AG0-s-p-500-equal-weight-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B16:B16" r:id="R18d1d209f77f4d53" display="https://etf.dws.com//en-gb/IE0002GFATQ6-s-p-500-equal-weight-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B17:B17" r:id="R49a03a2252b347ce" display="https://etf.dws.com//en-gb/IE0002PGSLZ5-us-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B18:B18" r:id="Re7cba68740ce4341" display="https://etf.dws.com//en-gb/IE0002ZM3JI1-usa-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B19:B19" r:id="R3fea905f7922412c" display="https://etf.dws.com//en-gb/IE00036F4K40-msci-global-sdg-3-good-health-ucits-etf-1c/"/>
+    <x:hyperlink ref="B20:B20" r:id="R224acbe2b9624a1c" display="https://etf.dws.com//en-gb/IE0003NQ0IY5-msci-world-quality-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B21:B21" r:id="R304048d64e6f4101" display="https://etf.dws.com//en-gb/IE0003W9O921-usd-corporate-green-bond-ucits-etf-2c/"/>
+    <x:hyperlink ref="B22:B22" r:id="R23d896f8de1d409a" display="https://etf.dws.com//en-gb/IE000472H9T4-nasdaq-100-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B23:B23" r:id="Rfd6b7677291a45c1" display="https://etf.dws.com//en-gb/IE0004KLW911-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1c/"/>
+    <x:hyperlink ref="B24:B24" r:id="Rfe65ad42d354402c" display="https://etf.dws.com//en-gb/IE0004MFRED4-s-p-500-equal-weight-scored-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B25:B25" r:id="R8503a52e7c7e4a48" display="https://etf.dws.com//en-gb/IE0004ZJGWT9-msci-europe-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B26:B26" r:id="Re8af77b8b2ad4b69" display="https://etf.dws.com//en-gb/IE0005E47AH7-msci-global-sdg-9-industry-innovation-infrastructure-ucits-etf-1c/"/>
+    <x:hyperlink ref="B27:B27" r:id="R1d805ab7ab364f33" display="https://etf.dws.com//en-gb/IE0006FDYJF8-msci-japan-climate-transition-ucits-etf-1d/"/>
+    <x:hyperlink ref="B28:B28" r:id="R49f2dd1d392f482f" display="https://etf.dws.com//en-gb/IE0006FFX5U1-msci-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B29:B29" r:id="R0d6f84905cd4457a" display="https://etf.dws.com//en-gb/IE0006GNB732-eur-high-yield-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B30:B30" r:id="R4d4fa0ebc4d745d1" display="https://etf.dws.com//en-gb/IE0006I3NZF8-msci-usa-consumer-discretionary-ucits-etf-1c/"/>
+    <x:hyperlink ref="B31:B31" r:id="R8b277532b2f44764" display="https://etf.dws.com//en-gb/IE0006WW1TQ4-msci-world-ex-usa-ucits-etf-1c/"/>
+    <x:hyperlink ref="B32:B32" r:id="Rf315f8f17b6d4d21" display="https://etf.dws.com//en-gb/IE0006YM7D84-usd-high-yield-corporate-bond-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B33:B33" r:id="R5c346ba4209541de" display="https://etf.dws.com//en-gb/IE00074JLU02-japan-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B34:B34" r:id="Rfbffe8d17d794cc9" display="https://etf.dws.com//en-gb/IE0007ULOZS8-s-p-500-scored-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B35:B35" r:id="Ra353aef197414a92" display="https://etf.dws.com//en-gb/IE0007WJ6B10-msci-global-clean-water-sanitation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B36:B36" r:id="Rfa1dba6185584cdc" display="https://etf.dws.com//en-gb/IE0008YN0OY8-msci-world-minimum-volatility-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B37:B37" r:id="R54a40b0630fe42f6" display="https://etf.dws.com//en-gb/IE00094GSCQ4-world-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B38:B38" r:id="R8ccd100f8772443a" display="https://etf.dws.com//en-gb/IE0009KLWT21-msci-world-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B39:B39" r:id="R0178da61810a40b3" display="https://etf.dws.com//en-gb/IE000BO2Y0T8-msci-nordic-ucits-etf-1c/"/>
+    <x:hyperlink ref="B40:B40" r:id="R2d8e80b667ca4ef5" display="https://etf.dws.com//en-gb/IE000CXLGK86-s-p-500-equal-weight-ucits-etf-2d/"/>
+    <x:hyperlink ref="B41:B41" r:id="Rec46187d01b64dff" display="https://etf.dws.com//en-gb/IE000DNSAS54-msci-emerging-markets-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B42:B42" r:id="Re29edb2344fd4a9d" display="https://etf.dws.com//en-gb/IE000DVHJV46-s-p-500-market-leaders-ucits-etf-1c/"/>
+    <x:hyperlink ref="B43:B43" r:id="Rb951a9e9917d40de" display="https://etf.dws.com//en-gb/IE000E0V65D8-world-biodiversity-focus-sri-ucits-etf-1c/"/>
+    <x:hyperlink ref="B44:B44" r:id="R7613a7ead64f4245" display="https://etf.dws.com//en-gb/IE000E4BATC9-msci-world-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B45:B45" r:id="R80fba34b8117494b" display="https://etf.dws.com//en-gb/IE000ER61U30-msci-europe-small-cap-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B46:B46" r:id="Rd232f4966b6641a2" display="https://etf.dws.com//en-gb/IE000EVOVOG1-msci-usa-positioning-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B47:B47" r:id="R7d4ea1d8d5ea4061" display="https://etf.dws.com//en-gb/IE000EXUE0G2-nasdaq-100-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B48:B48" r:id="R5d762481db2e4f7b" display="https://etf.dws.com//en-gb/IE000F04HGE5-floating-rate-notes-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B49:B49" r:id="Raea5aacf88224b70" display="https://etf.dws.com//en-gb/IE000F354Q61-msci-world-small-cap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B50:B50" r:id="Rc25ef3bb430743b0" display="https://etf.dws.com//en-gb/IE000FL46JJ1-s-p-500-equal-weight-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B51:B51" r:id="Ref64a8379a644b5a" display="https://etf.dws.com//en-gb/IE000FO05UG4-s-p-500-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B52:B52" r:id="R77592140ac0b405c" display="https://etf.dws.com//en-gb/IE000FO1A5D1-s-p-500-equal-weight-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B53:B53" r:id="Ree7b006dd16a41fe" display="https://etf.dws.com//en-gb/IE000FW16TX1-msci-usa-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B54:B54" r:id="Rc95023216fcf4fab" display="https://etf.dws.com//en-gb/IE000GF6QTP6-s-p-500-equal-weight-scored-screened-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B55:B55" r:id="R369a1977387541f6" display="https://etf.dws.com//en-gb/IE000GWA2J58-msci-emerging-markets-ucits-etf-1d/"/>
+    <x:hyperlink ref="B56:B56" r:id="Rd66560af5c0c4fad" display="https://etf.dws.com//en-gb/IE000GYDNJS5-msci-usa-climate-transition-ucits-etf-1d/"/>
+    <x:hyperlink ref="B57:B57" r:id="R095ecac36bac43b6" display="https://etf.dws.com//en-gb/IE000HT7E0B1-nordic-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B58:B58" r:id="Rd4166d39b2904060" display="https://etf.dws.com//en-gb/IE000HY30YW6-s-p-500-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B59:B59" r:id="R07adf6476d92479a" display="https://etf.dws.com//en-gb/IE000IDLWOL4-s-p-500-equal-weight-scored-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B60:B60" r:id="R335559c590464896" display="https://etf.dws.com//en-gb/IE000INYW0A7-msci-world-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B61:B61" r:id="R7cc39286acd3465a" display="https://etf.dws.com//en-gb/IE000ISS8DB2-msci-world-small-cap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B62:B62" r:id="R97f45db7ff5941ab" display="https://etf.dws.com//en-gb/IE000JZYIUN0-msci-global-sdg-7-affordable-and-clean-energy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B63:B63" r:id="Rd58442bf4fbe4dfa" display="https://etf.dws.com//en-gb/IE000KD0BZ68-msci-genomic-healthcare-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B64:B64" r:id="Rd88132e62fe94ddf" display="https://etf.dws.com//en-gb/IE000L2IS494-msci-global-social-fairness-contributors-ucits-etf-1c/"/>
+    <x:hyperlink ref="B65:B65" r:id="R0cca4d66722c48f2" display="https://etf.dws.com//en-gb/IE000L6ZMMC4-ftse-all-world-ucits-etf-1c/"/>
+    <x:hyperlink ref="B66:B66" r:id="R16ad24f925b043f7" display="https://etf.dws.com//en-gb/IE000LAUZQT6-msci-world-value-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B67:B67" r:id="R31bdb2d4904342df" display="https://etf.dws.com//en-gb/IE000LOSV2D0-usa-biodiversity-focus-sri-ucits-etf-1c/"/>
+    <x:hyperlink ref="B68:B68" r:id="Rabc8d1b13b0e4508" display="https://etf.dws.com//en-gb/IE000M8F3JA6-global-growth-leaders-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B69:B69" r:id="R82195cb0af7e4adf" display="https://etf.dws.com//en-gb/IE000MCVFK47-eur-corporate-green-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B70:B70" r:id="R73fd159518b545ac" display="https://etf.dws.com//en-gb/IE000MF9SZ46-msci-nordic-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B71:B71" r:id="Rebb3c7b15bc4489d" display="https://etf.dws.com//en-gb/IE000N5GJDD7-s-p-500-equal-weight-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B72:B72" r:id="Redc66a0712004e2a" display="https://etf.dws.com//en-gb/IE000N9MLVT1-msci-europe-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B73:B73" r:id="Rb624df02c72f4865" display="https://etf.dws.com//en-gb/IE000NS5HRY9-msci-world-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B74:B74" r:id="R8174d3f4f38f4a71" display="https://etf.dws.com//en-gb/IE000O7Q2E56-electrification-technologies-smart-grid-ucits-etf-1c/"/>
+    <x:hyperlink ref="B75:B75" r:id="R3574829a51264feb" display="https://etf.dws.com//en-gb/IE000ONQ3X90-msci-world-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B76:B76" r:id="R80e182951a684a0b" display="https://etf.dws.com//en-gb/IE000P4AYI47-msci-world-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B77:B77" r:id="R9e46e21c14e7418e" display="https://etf.dws.com//en-gb/IE000PDUVTF3-msci-usa-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B78:B78" r:id="R58a31344c8d84746" display="https://etf.dws.com//en-gb/IE000PSF3A70-msci-global-sdgs-ucits-etf-1c/"/>
+    <x:hyperlink ref="B79:B79" r:id="Re944c916f4374979" display="https://etf.dws.com//en-gb/IE000QVYFUT7-india-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B80:B80" r:id="R9ee895e606804ce7" display="https://etf.dws.com//en-gb/IE000RNHIKK1-msci-usa-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B81:B81" r:id="Rbf583511e7a34d7f" display="https://etf.dws.com//en-gb/IE000SRQBBT6-s-p-500-defensive-shareholder-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B82:B82" r:id="Rc9ff3b71d6724ad0" display="https://etf.dws.com//en-gb/IE000SZ25OI0-s-p-500-equal-weight-scored-screened-ucits-etf-4c-gbp-hedged/"/>
+    <x:hyperlink ref="B83:B83" r:id="R406a9365c2c249e8" display="https://etf.dws.com//en-gb/IE000TL3PL69-msci-world-momentum-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B84:B84" r:id="R126a6be02a6a4c6d" display="https://etf.dws.com//en-gb/IE000TSML5I8-msci-usa-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B85:B85" r:id="R601970cc75594c6d" display="https://etf.dws.com//en-gb/IE000TZT8TI0-emerging-markets-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B86:B86" r:id="R631fd318f284408e" display="https://etf.dws.com//en-gb/IE000UATQPE2-msci-world-small-cap-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B87:B87" r:id="R480e116cbcd44d90" display="https://etf.dws.com//en-gb/IE000UMV0L21-msci-usa-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B88:B88" r:id="Rd4c7ece1f94f459f" display="https://etf.dws.com//en-gb/IE000UP2BIZ9-s-p-500-ucits-etf-4d/"/>
+    <x:hyperlink ref="B89:B89" r:id="R76a4d61e236b4682" display="https://etf.dws.com//en-gb/IE000UX5WPU4-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1c/"/>
+    <x:hyperlink ref="B90:B90" r:id="R0668b7608d5d401d" display="https://etf.dws.com//en-gb/IE000UZCJS58-world-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B91:B91" r:id="R1af2b377112f4d43" display="https://etf.dws.com//en-gb/IE000V04SL39-msci-usa-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B92:B92" r:id="R5f103c2f3f074052" display="https://etf.dws.com//en-gb/IE000V0GDVU7-msci-global-sdg-11-sustainable-cities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B93:B93" r:id="R579e7740f47644fc" display="https://etf.dws.com//en-gb/IE000VCBWFL8-msci-emu-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B94:B94" r:id="R34df8c273e444f8f" display="https://etf.dws.com//en-gb/IE000VXC51U5-msci-ac-world-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B95:B95" r:id="R5e84d2f44ae24435" display="https://etf.dws.com//en-gb/IE000W6L2AI3-msci-emu-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B96:B96" r:id="R6f8393f8cd71401c" display="https://etf.dws.com//en-gb/IE000WGF1X01-msci-ac-world-screened-ucits-etf-5c-usd-hedged/"/>
+    <x:hyperlink ref="B97:B97" r:id="R851430970acb4491" display="https://etf.dws.com//en-gb/IE000WHO5BF2-usd-high-yield-corporate-bond-screened-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B98:B98" r:id="R35ae3e6148fd4e6e" display="https://etf.dws.com//en-gb/IE000WQ16XQ4-msci-europe-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B99:B99" r:id="R0881c3c8e2bc40bd" display="https://etf.dws.com//en-gb/IE000X1GW0A7-msci-world-imi-ucits-etf-1c/"/>
+    <x:hyperlink ref="B100:B100" r:id="R27db67668b2340fb" display="https://etf.dws.com//en-gb/IE000X4A4GV2-global-equity-top-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B101:B101" r:id="R4ab1ce2aaa704a3f" display="https://etf.dws.com//en-gb/IE000X5MRP46-msci-usa-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B102:B102" r:id="R4019dcdc83ea40ac" display="https://etf.dws.com//en-gb/IE000X63FXN4-usd-corporate-green-bond-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B103:B103" r:id="R4ffbe4099c7f4616" display="https://etf.dws.com//en-gb/IE000X6Z71P5-msci-usa-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B104:B104" r:id="R0f3bc433ee2a43a2" display="https://etf.dws.com//en-gb/IE000XOQ9TK4-msci-next-generation-internet-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B105:B105" r:id="R1d747d4bd4794bcd" display="https://etf.dws.com//en-gb/IE000Y6L6LE6-emu-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B106:B106" r:id="R7b91e3651b2d420d" display="https://etf.dws.com//en-gb/IE000Y6ZXZ48-msci-global-circular-economy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B107:B107" r:id="R961f18e1a8b149b3" display="https://etf.dws.com//en-gb/IE000YDOORK7-msci-fintech-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B108:B108" r:id="R552691d21bcd48bd" display="https://etf.dws.com//en-gb/IE000YKHGYN2-ftse-all-world-ex-us-ucits-etf-1c/"/>
+    <x:hyperlink ref="B109:B109" r:id="Rb5e908ec259142dc" display="https://etf.dws.com//en-gb/IE000Z0FC0G5-msci-world-ex-usa-ucits-etf-1d/"/>
+    <x:hyperlink ref="B110:B110" r:id="R48ac34e168754532" display="https://etf.dws.com//en-gb/IE000Z9SJA06-s-p-500-ucits-etf-4c/"/>
+    <x:hyperlink ref="B111:B111" r:id="R8e54075665524230" display="https://etf.dws.com//en-gb/IE00B3Y8D011-portfolio-income-ucits-etf-1d/"/>
+    <x:hyperlink ref="B112:B112" r:id="Ref3cbfbfa1444b2e" display="https://etf.dws.com//en-gb/IE00B8KMSQ34-s-p-500-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B113:B113" r:id="Rc407b750fe734ad1" display="https://etf.dws.com//en-gb/IE00B9MRHC27-msci-nordic-ucits-etf-1d/"/>
+    <x:hyperlink ref="B114:B114" r:id="R283f2efee9254844" display="https://etf.dws.com//en-gb/IE00B9MRJJ36-mdax-esg-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B115:B115" r:id="R9ab8ae3ca44f4b08" display="https://etf.dws.com//en-gb/IE00BCHWNQ94-msci-world-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B116:B116" r:id="R2d8ed92a7c674743" display="https://etf.dws.com//en-gb/IE00BCHWNS19-msci-usa-energy-ucits-etf-1d/"/>
+    <x:hyperlink ref="B117:B117" r:id="R6162768bec4a4249" display="https://etf.dws.com//en-gb/IE00BCHWNT26-msci-usa-financials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B118:B118" r:id="Rc6dd47ca60404e68" display="https://etf.dws.com//en-gb/IE00BCHWNV48-msci-usa-industrials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B119:B119" r:id="R91d415d0ed2047c1" display="https://etf.dws.com//en-gb/IE00BCHWNW54-msci-usa-health-care-ucits-etf-1d/"/>
+    <x:hyperlink ref="B120:B120" r:id="R004bbed1de31488c" display="https://etf.dws.com//en-gb/IE00BD4DX952-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1d/"/>
+    <x:hyperlink ref="B121:B121" r:id="Rda3f37d9bea44d23" display="https://etf.dws.com//en-gb/IE00BD4DXB77-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B122:B122" r:id="Rcbae77a20bf64f80" display="https://etf.dws.com//en-gb/IE00BDB7J586-msci-usa-minimum-volatility-ucits-etf-1d/"/>
+    <x:hyperlink ref="B123:B123" r:id="Ref423d534c544126" display="https://etf.dws.com//en-gb/IE00BDGN9Z19-msci-emu-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B124:B124" r:id="R0e5e7bd01df84799" display="https://etf.dws.com//en-gb/IE00BDR5HM97-usd-high-yield-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B125:B125" r:id="Rec06943e15e84f7e" display="https://etf.dws.com//en-gb/IE00BDR5HN05-usd-high-yield-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B126:B126" r:id="Ra1760cb36b354e13" display="https://etf.dws.com//en-gb/IE00BDVPTJ63-msci-usa-banks-ucits-etf-1d/"/>
+    <x:hyperlink ref="B127:B127" r:id="R1ae59c50349e49df" display="https://etf.dws.com//en-gb/IE00BF8J5974-usd-corporate-bond-short-duration-sri-pab-ucits-etf-1d/"/>
+    <x:hyperlink ref="B128:B128" r:id="R1822afcd3f9843f7" display="https://etf.dws.com//en-gb/IE00BFMKQ930-usd-corporate-bond-short-duration-sri-pab-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B129:B129" r:id="R7277af837eb749e5" display="https://etf.dws.com//en-gb/IE00BFMKQC67-usd-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B130:B130" r:id="Rb07d8fb5a3ae4251" display="https://etf.dws.com//en-gb/IE00BFMNHK08-msci-europe-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B131:B131" r:id="R032699e9d88349e2" display="https://etf.dws.com//en-gb/IE00BFMNPS42-msci-usa-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B132:B132" r:id="R0b4f2a79fde3474a" display="https://etf.dws.com//en-gb/IE00BG04LT92-usd-high-yield-corporate-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B133:B133" r:id="Re1aa6c08809744ff" display="https://etf.dws.com//en-gb/IE00BG04LV15-usd-high-yield-corporate-bond-ucits-etf-4d-gbp-hedged/"/>
+    <x:hyperlink ref="B134:B134" r:id="Rd96f5795fb104b33" display="https://etf.dws.com//en-gb/IE00BG04LY46-usd-corporate-bond-ucits-etf-5d-gbp-hedged/"/>
+    <x:hyperlink ref="B135:B135" r:id="R03a15af23c6d4ca0" display="https://etf.dws.com//en-gb/IE00BG04LZ52-msci-usa-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B136:B136" r:id="R764e26287af74980" display="https://etf.dws.com//en-gb/IE00BG04M077-msci-usa-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B137:B137" r:id="R77d60d938e6a4111" display="https://etf.dws.com//en-gb/IE00BG36TC12-msci-japan-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B138:B138" r:id="R7a8c10cb79fa4e2c" display="https://etf.dws.com//en-gb/IE00BG370F43-msci-emerging-markets-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B139:B139" r:id="R598cbe3252c84730" display="https://etf.dws.com//en-gb/IE00BGHQ0G80-msci-ac-world-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B140:B140" r:id="R722047821d104c53" display="https://etf.dws.com//en-gb/IE00BGJWX091-s-p-500-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B141:B141" r:id="R4e2677fa4a4d4c5e" display="https://etf.dws.com//en-gb/IE00BGQYRQ28-msci-usa-consumer-staples-ucits-etf-1d/"/>
+    <x:hyperlink ref="B142:B142" r:id="R5717056d6ad54142" display="https://etf.dws.com//en-gb/IE00BGQYRR35-msci-usa-consumer-discretionary-ucits-etf-1d/"/>
+    <x:hyperlink ref="B143:B143" r:id="R251ffc74775d440b" display="https://etf.dws.com//en-gb/IE00BGQYRS42-msci-usa-information-technology-ucits-etf-1d/"/>
+    <x:hyperlink ref="B144:B144" r:id="R3208a78aa5814df3" display="https://etf.dws.com//en-gb/IE00BGV5VM45-s-p-europe-ex-uk-ucits-etf-1d/"/>
+    <x:hyperlink ref="B145:B145" r:id="R3aed77df2b2f4b67" display="https://etf.dws.com//en-gb/IE00BGV5VN51-artificial-intelligence-big-data-ucits-etf-1c/"/>
+    <x:hyperlink ref="B146:B146" r:id="R80b3239f3d8c4a49" display="https://etf.dws.com//en-gb/IE00BGV5VR99-future-mobility-ucits-etf-1c/"/>
+    <x:hyperlink ref="B147:B147" r:id="R7a163b986d4246c9" display="https://etf.dws.com//en-gb/IE00BH361H73-msci-north-america-high-dividend-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B148:B148" r:id="Rb6506a8bdf9a4436" display="https://etf.dws.com//en-gb/IE00BJ0KDQ92-msci-world-ucits-etf-1c/"/>
+    <x:hyperlink ref="B149:B149" r:id="R8564d53e7cb847fe" display="https://etf.dws.com//en-gb/IE00BJ0KDR00-msci-usa-ucits-etf-1c/"/>
+    <x:hyperlink ref="B150:B150" r:id="R9eb75a7d0214448d" display="https://etf.dws.com//en-gb/IE00BJZ2DC62-msci-usa-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B151:B151" r:id="R1745c9b1135a4c1f" display="https://etf.dws.com//en-gb/IE00BJZ2DD79-russell-2000-ucits-etf-1c/"/>
+    <x:hyperlink ref="B152:B152" r:id="R1860852858e14b7d" display="https://etf.dws.com//en-gb/IE00BK1PV445-msci-usa-ucits-etf-1d/"/>
+    <x:hyperlink ref="B153:B153" r:id="Rdcdf4e13268847a5" display="https://etf.dws.com//en-gb/IE00BK1PV551-msci-world-ucits-etf-1d/"/>
+    <x:hyperlink ref="B154:B154" r:id="R8d2f1bf8fc8547e9" display="https://etf.dws.com//en-gb/IE00BL25JL35-msci-world-quality-ucits-etf-1c/"/>
+    <x:hyperlink ref="B155:B155" r:id="R5a9c893fb3cf4b94" display="https://etf.dws.com//en-gb/IE00BL25JM42-msci-world-value-ucits-etf-1c/"/>
+    <x:hyperlink ref="B156:B156" r:id="R283bfa057cc94059" display="https://etf.dws.com//en-gb/IE00BL25JN58-msci-world-minimum-volatility-ucits-etf-1c/"/>
+    <x:hyperlink ref="B157:B157" r:id="R1ffb05fa2c7244a0" display="https://etf.dws.com//en-gb/IE00BL25JP72-msci-world-momentum-ucits-etf-1c/"/>
+    <x:hyperlink ref="B158:B158" r:id="R1206dc350e834fd1" display="https://etf.dws.com//en-gb/IE00BL58LJ19-usd-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B159:B159" r:id="Rd191380fe1af4c7d" display="https://etf.dws.com//en-gb/IE00BL58LL31-usd-corporate-bond-sri-pab-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B160:B160" r:id="R77e180fd04ea4828" display="https://etf.dws.com//en-gb/IE00BLNMYC90-s-p-500-equal-weight-ucits-etf-1c/"/>
+    <x:hyperlink ref="B161:B161" r:id="Rc198bb585f6e448b" display="https://etf.dws.com//en-gb/IE00BM67HJ62-msci-emerging-markets-ex-china-ucits-etf-1c/"/>
+    <x:hyperlink ref="B162:B162" r:id="R88a1319d13014d4f" display="https://etf.dws.com//en-gb/IE00BM67HK77-msci-world-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B163:B163" r:id="Rdc9481e85ddf418a" display="https://etf.dws.com//en-gb/IE00BM67HL84-msci-world-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B164:B164" r:id="R245ea0173cba4cba" display="https://etf.dws.com//en-gb/IE00BM67HM91-msci-world-energy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B165:B165" r:id="Rd2d7ba647b24494b" display="https://etf.dws.com//en-gb/IE00BM67HN09-msci-world-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B166:B166" r:id="R9d31b23d71784ab5" display="https://etf.dws.com//en-gb/IE00BM67HP23-msci-world-consumer-discretionary-ucits-etf-1c/"/>
+    <x:hyperlink ref="B167:B167" r:id="Rcc19318ebc3a4a65" display="https://etf.dws.com//en-gb/IE00BM67HQ30-msci-world-utilities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B168:B168" r:id="R281b9a1372ff40ef" display="https://etf.dws.com//en-gb/IE00BM67HR47-msci-world-communication-services-ucits-etf-1c/"/>
+    <x:hyperlink ref="B169:B169" r:id="Rb6d88d2d090d482b" display="https://etf.dws.com//en-gb/IE00BM67HS53-msci-world-materials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B170:B170" r:id="R8863d1f093aa43ba" display="https://etf.dws.com//en-gb/IE00BM67HT60-msci-world-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B171:B171" r:id="R91fa92792d834d33" display="https://etf.dws.com//en-gb/IE00BM67HV82-msci-world-industrials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B172:B172" r:id="R0d5158d5219d48e8" display="https://etf.dws.com//en-gb/IE00BM67HW99-s-p-500-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B173:B173" r:id="R8b7ce95f3e904976" display="https://etf.dws.com//en-gb/IE00BM67HX07-s-p-500-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B174:B174" r:id="R397302a8849b44b5" display="https://etf.dws.com//en-gb/IE00BM97MR69-us-treasuries-ultrashort-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B175:B175" r:id="R9b5f4b06fd8e491e" display="https://etf.dws.com//en-gb/IE00BM97MV06-us-treasuries-ultrashort-bond-ucits-etf-3c-mxn-hedged/"/>
+    <x:hyperlink ref="B176:B176" r:id="Rd133a3571e5c489b" display="https://etf.dws.com//en-gb/IE00BMCFJ320-usd-corporate-bond-ucits-etf-6c-mxn-hedged/"/>
+    <x:hyperlink ref="B177:B177" r:id="R7fc3017ad03245aa" display="https://etf.dws.com//en-gb/IE00BMFKG444-nasdaq-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B178:B178" r:id="R3004805cef764e5d" display="https://etf.dws.com//en-gb/IE00BMY76136-msci-world-esg-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B179:B179" r:id="R9e2289ca383d47d0" display="https://etf.dws.com//en-gb/IE00BN2BCY94-developed-green-real-estate-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B180:B180" r:id="R15fcf3b859fc4870" display="https://etf.dws.com//en-gb/IE00BNC1G699-msci-emu-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B181:B181" r:id="R6b8de9b16ff14d44" display="https://etf.dws.com//en-gb/IE00BNC1G707-msci-usa-communication-services-ucits-etf-1d/"/>
+    <x:hyperlink ref="B182:B182" r:id="Ra5e3960cb82f4768" display="https://etf.dws.com//en-gb/IE00BNKF6C99-stoxx-european-market-leaders-ucits-etf-1c/"/>
+    <x:hyperlink ref="B183:B183" r:id="Rcb051a86c66b422c" display="https://etf.dws.com//en-gb/IE00BP8FKB21-ftse-developed-europe-ex-uk-real-estate-ucits-etf-1c/"/>
+    <x:hyperlink ref="B184:B184" r:id="Rf9fb62ea99de4c0b" display="https://etf.dws.com//en-gb/IE00BPVLQD13-msci-japan-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B185:B185" r:id="Rd4b00243e2f5469e" display="https://etf.dws.com//en-gb/IE00BPVLQF37-msci-japan-screened-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B186:B186" r:id="R23f66c8ca45b47fc" display="https://etf.dws.com//en-gb/IE00BQXKVQ19-msci-gcc-select-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B187:B187" r:id="R215648d8f54b474f" display="https://etf.dws.com//en-gb/IE00BRB36B93-msci-japan-screened-ucits-etf-3c-eur-hedged/"/>
+    <x:hyperlink ref="B188:B188" r:id="R69a356b30f6042df" display="https://etf.dws.com//en-gb/IE00BTGD1B38-msci-japan-screened-ucits-etf-4c-usd-hedged/"/>
+    <x:hyperlink ref="B189:B189" r:id="R5a708cbddbdd42e3" display="https://etf.dws.com//en-gb/IE00BTJRMP35-msci-emerging-markets-ucits-etf-1c/"/>
+    <x:hyperlink ref="B190:B190" r:id="R4843fc5a6a874842" display="https://etf.dws.com//en-gb/IE00BYPHT736-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1d/"/>
+    <x:hyperlink ref="B191:B191" r:id="R7eb72d9ce13245ef" display="https://etf.dws.com//en-gb/IE00BYZNF849-global-infrastructure-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B192:B192" r:id="R4f1f16ad5e364322" display="https://etf.dws.com//en-gb/IE00BZ02LR44-msci-world-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B193:B193" r:id="Ra4087e0b785b4cb1" display="https://etf.dws.com//en-gb/IE00BZ036H21-usd-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B194:B194" r:id="R40239eb9bf394921" display="https://etf.dws.com//en-gb/IE00BZ036J45-usd-corporate-bond-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B195:B195" r:id="Rff56acd6eac34d63" display="https://etf.dws.com//en-gb/IE00BZ1BS790-msci-world-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B196:B196" r:id="R227957eb24c5451f" display="https://etf.dws.com//en-gb/LU0274208692-msci-world-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B197:B197" r:id="Rdf8fa832ba554b45" display="https://etf.dws.com//en-gb/LU0274209237-msci-europe-ucits-etf-1c/"/>
+    <x:hyperlink ref="B198:B198" r:id="R49b8a9b4420b408d" display="https://etf.dws.com//en-gb/LU0274209740-msci-japan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B199:B199" r:id="Ree092049ecb14561" display="https://etf.dws.com//en-gb/LU0274210672-msci-usa-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B200:B200" r:id="Rd1ce7d5c584e4557" display="https://etf.dws.com//en-gb/LU0274211217-euro-stoxx-50-ucits-etf-1d/"/>
+    <x:hyperlink ref="B201:B201" r:id="Rc4fcd75636174569" display="https://etf.dws.com//en-gb/LU0274211480-dax-ucits-etf-1c/"/>
+    <x:hyperlink ref="B202:B202" r:id="Rfa0175714e5a4b5e" display="https://etf.dws.com//en-gb/LU0274212538-ftse-mib-ucits-etf-1d/"/>
+    <x:hyperlink ref="B203:B203" r:id="R82234c93dfcd414e" display="https://etf.dws.com//en-gb/LU0274221281-switzerland-ucits-etf-1d/"/>
+    <x:hyperlink ref="B204:B204" r:id="Rcd86cbe0cc594dd5" display="https://etf.dws.com//en-gb/LU0290355717-eurozone-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B205:B205" r:id="R5d9371d83cfd4a3d" display="https://etf.dws.com//en-gb/LU0290356871-eurozone-government-bond-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B206:B206" r:id="R2fc3422a7f2f4f2f" display="https://etf.dws.com//en-gb/LU0290356954-eurozone-government-bond-3-5-ucits-etf-1c/"/>
+    <x:hyperlink ref="B207:B207" r:id="Rc544f6e822864a3d" display="https://etf.dws.com//en-gb/LU0290357176-eurozone-government-bond-5-7-ucits-etf-1c/"/>
+    <x:hyperlink ref="B208:B208" r:id="R83451693238f4989" display="https://etf.dws.com//en-gb/LU0290357259-eurozone-government-bond-7-10-ucits-etf-1c/"/>
+    <x:hyperlink ref="B209:B209" r:id="R2d4c26817f674af3" display="https://etf.dws.com//en-gb/LU0290357507-eurozone-government-bond-15-30-ucits-etf-1c/"/>
+    <x:hyperlink ref="B210:B210" r:id="R459c5bb63005438c" display="https://etf.dws.com//en-gb/LU0290357846-eurozone-government-bond-25-ucits-etf-1c/"/>
+    <x:hyperlink ref="B211:B211" r:id="R50d69d04d1c1429e" display="https://etf.dws.com//en-gb/LU0290357929-global-inflation-linked-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B212:B212" r:id="Re2319110b1564cf0" display="https://etf.dws.com//en-gb/LU0290358224-eurozone-inflation-linked-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B213:B213" r:id="Raf231c990ff740f5" display="https://etf.dws.com//en-gb/LU0290358497-eur-overnight-rate-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B214:B214" r:id="R61431c994dc84918" display="https://etf.dws.com//en-gb/LU0292095535-euro-stoxx-quality-dividend-ucits-etf-1d/"/>
+    <x:hyperlink ref="B215:B215" r:id="R77d6e226be974a0b" display="https://etf.dws.com//en-gb/LU0292096186-stoxx-global-select-dividend-100-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B216:B216" r:id="Rb1a33e07182d4cbe" display="https://etf.dws.com//en-gb/LU0292097234-ftse-100-income-ucits-etf-1d/"/>
+    <x:hyperlink ref="B217:B217" r:id="R92c0c9d400c7466a" display="https://etf.dws.com//en-gb/LU0292097317-ftse-250-ucits-etf-1d/"/>
+    <x:hyperlink ref="B218:B218" r:id="R40a2b9f236444de2" display="https://etf.dws.com//en-gb/LU0292097747-msci-uk-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B219:B219" r:id="Rbc99b67ceaf44662" display="https://etf.dws.com//en-gb/LU0292100046-msci-korea-ucits-etf-1c/"/>
+    <x:hyperlink ref="B220:B220" r:id="R46857e6a5a3b4773" display="https://etf.dws.com//en-gb/LU0292100806-msci-europe-materials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B221:B221" r:id="Rbe9fc7de2be9416e" display="https://etf.dws.com//en-gb/LU0292103222-msci-europe-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B222:B222" r:id="R64b29c3064a84a35" display="https://etf.dws.com//en-gb/LU0292103651-msci-europe-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B223:B223" r:id="Rf345f49c4d50451c" display="https://etf.dws.com//en-gb/LU0292104030-msci-europe-communication-services-ucits-etf-1c/"/>
+    <x:hyperlink ref="B224:B224" r:id="R89bac47c5d5f452b" display="https://etf.dws.com//en-gb/LU0292104469-msci-europe-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B225:B225" r:id="R44fda2e47e854d7e" display="https://etf.dws.com//en-gb/LU0292104899-msci-europe-utilities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B226:B226" r:id="Re8e8f5917045431b" display="https://etf.dws.com//en-gb/LU0292105359-msci-europe-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B227:B227" r:id="R5323864e84784ba7" display="https://etf.dws.com//en-gb/LU0292106084-msci-europe-industrials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B228:B228" r:id="R8e029e5097a64ed1" display="https://etf.dws.com//en-gb/LU0292106167-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B229:B229" r:id="R5cb27e6efab24615" display="https://etf.dws.com//en-gb/LU0292106241-shortdax-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B230:B230" r:id="R6ea76fd9069d41a7" display="https://etf.dws.com//en-gb/LU0292106753-euro-stoxx-50-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B231:B231" r:id="R77da4da14fc7420c" display="https://etf.dws.com//en-gb/LU0292107645-msci-emerging-markets-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B232:B232" r:id="R5539a98de99d4869" display="https://etf.dws.com//en-gb/LU0292107991-msci-em-asia-screened-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B233:B233" r:id="R737a7370de844f81" display="https://etf.dws.com//en-gb/LU0292108619-msci-em-latin-america-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B234:B234" r:id="R1645af99ddf64342" display="https://etf.dws.com//en-gb/LU0292109005-msci-em-europe-middle-east-africa-esg-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B235:B235" r:id="Rb1f3461281614658" display="https://etf.dws.com//en-gb/LU0292109187-msci-taiwan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B236:B236" r:id="Rb119a0d5d13840b7" display="https://etf.dws.com//en-gb/LU0292109344-msci-brazil-ucits-etf-1c/"/>
+    <x:hyperlink ref="B237:B237" r:id="Racfa12fdf79f4e96" display="https://etf.dws.com//en-gb/LU0292109690-nifty-50-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B238:B238" r:id="R461dad56ca784363" display="https://etf.dws.com//en-gb/LU0292109856-msci-china-a-ucits-etf-1c/"/>
+    <x:hyperlink ref="B239:B239" r:id="R85564d891b7e4e5f" display="https://etf.dws.com//en-gb/LU0321462870-itraxx-crossover-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B240:B240" r:id="Rf45a9377aec34d78" display="https://etf.dws.com//en-gb/LU0321462953-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B241:B241" r:id="R98ecac38c6e64a27" display="https://etf.dws.com//en-gb/LU0321464652-gbp-overnight-rate-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B242:B242" r:id="R7c092d04018a4057" display="https://etf.dws.com//en-gb/LU0321465469-usd-overnight-rate-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B243:B243" r:id="Rc5f155905a4b4915" display="https://etf.dws.com//en-gb/LU0322248146-sli-ucits-etf-1d/"/>
+    <x:hyperlink ref="B244:B244" r:id="R4af380fb4ba84b65" display="https://etf.dws.com//en-gb/LU0322250712-lpx-private-equity-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B245:B245" r:id="Rd75c3d8f7685440f" display="https://etf.dws.com//en-gb/LU0322250985-cac-40-ucits-etf-1d/"/>
+    <x:hyperlink ref="B246:B246" r:id="R88d7b5920c834aab" display="https://etf.dws.com//en-gb/LU0322251520-s-p-500-inverse-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B247:B247" r:id="R470d6b78759a478c" display="https://etf.dws.com//en-gb/LU0322252171-msci-ac-asia-ex-japan-esg-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B248:B248" r:id="R9785513d4d504989" display="https://etf.dws.com//en-gb/LU0322252338-msci-pacific-ex-japan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B249:B249" r:id="Ra66db9b2319b45c9" display="https://etf.dws.com//en-gb/LU0322252924-vietnam-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B250:B250" r:id="R32018795785a4eb1" display="https://etf.dws.com//en-gb/LU0322253229-s-p-global-infrastructure-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B251:B251" r:id="Rf3eccec66d664fd4" display="https://etf.dws.com//en-gb/LU0322253732-msci-europe-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B252:B252" r:id="Rc2fa5c14d24049e3" display="https://etf.dws.com//en-gb/LU0322253906-msci-europe-small-cap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B253:B253" r:id="Rd78d91bb26ac442f" display="https://etf.dws.com//en-gb/LU0328473581-ftse-100-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B254:B254" r:id="Rd9e3a9eefd25408d" display="https://etf.dws.com//en-gb/LU0328474803-s-p-asx-200-ucits-etf-1d/"/>
+    <x:hyperlink ref="B255:B255" r:id="Rd0387e6b807a485d" display="https://etf.dws.com//en-gb/LU0328475792-stoxx-europe-600-ucits-etf-1c/"/>
+    <x:hyperlink ref="B256:B256" r:id="Rf5141a7b7ddb4b69" display="https://etf.dws.com//en-gb/LU0328476410-s-p-select-frontier-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B257:B257" r:id="Ra86cafdf509f4117" display="https://etf.dws.com//en-gb/LU0335044896-eur-overnight-rate-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B258:B258" r:id="R7500f2ffa28a4e2c" display="https://etf.dws.com//en-gb/LU0378818131-global-government-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B259:B259" r:id="Rec11f789d14e456f" display="https://etf.dws.com//en-gb/LU0378818560-singapore-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B260:B260" r:id="R98039838e3c64737" display="https://etf.dws.com//en-gb/LU0380865021-euro-stoxx-50-ucits-etf-1c/"/>
+    <x:hyperlink ref="B261:B261" r:id="Rb2e92b53b10c466e" display="https://etf.dws.com//en-gb/LU0397221945-portfolio-ucits-etf-1c/"/>
+    <x:hyperlink ref="B262:B262" r:id="Rb6664a8472d94f80" display="https://etf.dws.com//en-gb/LU0411075020-shortdax-x2-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B263:B263" r:id="R66e652c8a3884556" display="https://etf.dws.com//en-gb/LU0411075376-levdax-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B264:B264" r:id="Rb39b4ae072da44e2" display="https://etf.dws.com//en-gb/LU0411078552-s-p-500-2x-leveraged-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B265:B265" r:id="Rb8d65b7b8c124246" display="https://etf.dws.com//en-gb/LU0411078636-s-p-500-2x-inverse-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B266:B266" r:id="R2fce13b5c9934d40" display="https://etf.dws.com//en-gb/LU0429458895-us-treasuries-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B267:B267" r:id="R3338b7a26e044d4d" display="https://etf.dws.com//en-gb/LU0429459356-us-treasuries-ucits-etf-1d/"/>
+    <x:hyperlink ref="B268:B268" r:id="R43aedfcdbe594cf5" display="https://etf.dws.com//en-gb/LU0429790743-bloomberg-commodity-swap-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B269:B269" r:id="Rb5dc02f0e7da424e" display="https://etf.dws.com//en-gb/LU0460391732-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-2c/"/>
+    <x:hyperlink ref="B270:B270" r:id="R99750075ba7446c9" display="https://etf.dws.com//en-gb/LU0460391906-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-3c-gbp-hedged/"/>
+    <x:hyperlink ref="B271:B271" r:id="Rdba113968e554b85" display="https://etf.dws.com//en-gb/LU0468896575-germany-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B272:B272" r:id="Rb71aa6591e574e6e" display="https://etf.dws.com//en-gb/LU0468897110-germany-government-bond-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B273:B273" r:id="Ra225e9a8def24287" display="https://etf.dws.com//en-gb/LU0476289466-msci-mexico-ucits-etf-1c/"/>
+    <x:hyperlink ref="B274:B274" r:id="R0d615ce204764d03" display="https://etf.dws.com//en-gb/LU0476289540-msci-canada-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B275:B275" r:id="Re3cb89a75dc84389" display="https://etf.dws.com//en-gb/LU0476289623-msci-indonesia-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B276:B276" r:id="R8edae69b63264c52" display="https://etf.dws.com//en-gb/LU0478205379-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B277:B277" r:id="R076f960b82a84da2" display="https://etf.dws.com//en-gb/LU0478205965-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B278:B278" r:id="Rd68bc1cd03ac488e" display="https://etf.dws.com//en-gb/LU0484968812-eur-corporate-bond-sri-pab-ucits-etf-1d/"/>
+    <x:hyperlink ref="B279:B279" r:id="R672545485bad49ec" display="https://etf.dws.com//en-gb/LU0484968903-eur-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B280:B280" r:id="R2d144bb0f89d4327" display="https://etf.dws.com//en-gb/LU0484969463-target-maturity-sept-2029-italy-and-spain-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B281:B281" r:id="R3b1ab871199c4cb7" display="https://etf.dws.com//en-gb/LU0486851024-msci-europe-value-ucits-etf-1c/"/>
+    <x:hyperlink ref="B282:B282" r:id="R7a24c9c5c1f24b56" display="https://etf.dws.com//en-gb/LU0489337690-ftse-developed-europe-real-estate-ucits-etf-1c/"/>
+    <x:hyperlink ref="B283:B283" r:id="Re48fe19586494bd8" display="https://etf.dws.com//en-gb/LU0490618542-s-p-500-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B284:B284" r:id="R1e7bb4d4a3b740f2" display="https://etf.dws.com//en-gb/LU0494592974-australia-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B285:B285" r:id="R032dc89e90aa426b" display="https://etf.dws.com//en-gb/LU0514694370-msci-malaysia-ucits-etf-1c/"/>
+    <x:hyperlink ref="B286:B286" r:id="R7196ff75dcfa472e" display="https://etf.dws.com//en-gb/LU0514694701-msci-thailand-ucits-etf-1c/"/>
+    <x:hyperlink ref="B287:B287" r:id="R6bf85205e8e446b5" display="https://etf.dws.com//en-gb/LU0514695187-msci-india-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B288:B288" r:id="R3ec419a0f6d14a07" display="https://etf.dws.com//en-gb/LU0514695690-msci-china-ucits-etf-1c/"/>
+    <x:hyperlink ref="B289:B289" r:id="R93c1d5946f6f4795" display="https://etf.dws.com//en-gb/LU0524480265-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1c/"/>
+    <x:hyperlink ref="B290:B290" r:id="R79a6b26643804bff" display="https://etf.dws.com//en-gb/LU0592215403-msci-philippines-ucits-etf-1c/"/>
+    <x:hyperlink ref="B291:B291" r:id="Rfdeadd5ae0e843a4" display="https://etf.dws.com//en-gb/LU0592216393-spain-ucits-etf-1c/"/>
+    <x:hyperlink ref="B292:B292" r:id="R51d4480c0e004e4f" display="https://etf.dws.com//en-gb/LU0592217524-msci-africa-top-50-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B293:B293" r:id="Re728c953bc744f9f" display="https://etf.dws.com//en-gb/LU0613540268-italy-government-bond-0-1-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B294:B294" r:id="R49fee96d7ef4488a" display="https://etf.dws.com//en-gb/LU0614173549-eurozone-government-bond-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B295:B295" r:id="Rf8cdd70816e14287" display="https://etf.dws.com//en-gb/LU0614173895-eurozone-government-bond-3-5-ucits-etf-1d/"/>
+    <x:hyperlink ref="B296:B296" r:id="Reb26b8858ea445b7" display="https://etf.dws.com//en-gb/LU0641006290-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B297:B297" r:id="R44b254f050484995" display="https://etf.dws.com//en-gb/LU0641006456-global-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B298:B298" r:id="R6f71c15ee75f4a6f" display="https://etf.dws.com//en-gb/LU0641006613-global-government-bond-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B299:B299" r:id="Rfc6b8a8f844d4e7f" display="https://etf.dws.com//en-gb/LU0641007009-global-inflation-linked-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B300:B300" r:id="R3ae0020fb8f14752" display="https://etf.dws.com//en-gb/LU0641007264-global-inflation-linked-bond-ucits-etf-3d-gbp-hedged/"/>
+    <x:hyperlink ref="B301:B301" r:id="Rb232253e82a84c21" display="https://etf.dws.com//en-gb/LU0641007421-global-inflation-linked-bond-ucits-etf-4d-chf-hedged/"/>
+    <x:hyperlink ref="B302:B302" r:id="Rc7f0404997d943b8" display="https://etf.dws.com//en-gb/LU0643975161-germany-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B303:B303" r:id="R150ff26c1de749b1" display="https://etf.dws.com//en-gb/LU0643975591-eurozone-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B304:B304" r:id="R9287a7b764c447e2" display="https://etf.dws.com//en-gb/LU0659578842-msci-singapore-ucits-etf-1c/"/>
+    <x:hyperlink ref="B305:B305" r:id="Re076057b724948e3" display="https://etf.dws.com//en-gb/LU0659579063-atx-ucits-etf-1c/"/>
+    <x:hyperlink ref="B306:B306" r:id="R3c8495d3376347bc" display="https://etf.dws.com//en-gb/LU0659579147-msci-pakistan-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B307:B307" r:id="R591f9428716e462b" display="https://etf.dws.com//en-gb/LU0659579733-msci-world-swap-ucits-etf-4c-eur-hedged/"/>
+    <x:hyperlink ref="B308:B308" r:id="Rc0f8ae00ad174572" display="https://etf.dws.com//en-gb/LU0659580079-msci-japan-ucits-etf-4c-eur-hedged/"/>
+    <x:hyperlink ref="B309:B309" r:id="R3348664168c74585" display="https://etf.dws.com//en-gb/LU0677077884-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2d/"/>
+    <x:hyperlink ref="B310:B310" r:id="R2519076a2ec146d8" display="https://etf.dws.com//en-gb/LU0690964092-global-government-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B311:B311" r:id="R6bf82392175c4c9d" display="https://etf.dws.com//en-gb/LU0779800910-csi300-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B312:B312" r:id="Re0f74c1bcca04c8f" display="https://etf.dws.com//en-gb/LU0838780707-ftse-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B313:B313" r:id="R16fef689dba54b18" display="https://etf.dws.com//en-gb/LU0838782315-dax-esg-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B314:B314" r:id="Red7b9855567a4336" display="https://etf.dws.com//en-gb/LU0839027447-nikkei-225-ucits-etf-1d/"/>
+    <x:hyperlink ref="B315:B315" r:id="R86861c3479114880" display="https://etf.dws.com//en-gb/LU0846194776-msci-emu-ucits-etf-1d/"/>
+    <x:hyperlink ref="B316:B316" r:id="R160d9a19e68a4c20" display="https://etf.dws.com//en-gb/LU0875160326-harvest-csi300-ucits-etf-1d/"/>
+    <x:hyperlink ref="B317:B317" r:id="Rf2d1062707bb4b14" display="https://etf.dws.com//en-gb/LU0908508731-global-government-bond-ucits-etf-5c/"/>
+    <x:hyperlink ref="B318:B318" r:id="R62e7205f15df41b6" display="https://etf.dws.com//en-gb/LU0908508814-global-inflation-linked-bond-ucits-etf-5c/"/>
+    <x:hyperlink ref="B319:B319" r:id="R04cfe2947880450c" display="https://etf.dws.com//en-gb/LU0925589839-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B320:B320" r:id="R81ab89e7e074490b" display="https://etf.dws.com//en-gb/LU0927735406-msci-japan-ucits-etf-2d-usd-hedged/"/>
+    <x:hyperlink ref="B321:B321" r:id="Rdf5a46a1d5c14499" display="https://etf.dws.com//en-gb/LU0942970103-esg-global-aggregate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B322:B322" r:id="Rf4e4cc08e342418e" display="https://etf.dws.com//en-gb/LU0942970285-esg-global-aggregate-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B323:B323" r:id="Re53b5ff46dd24d12" display="https://etf.dws.com//en-gb/LU0942970368-esg-global-aggregate-bond-ucits-etf-3d-gbp-hedged/"/>
+    <x:hyperlink ref="B324:B324" r:id="R60ecd9370b6f466e" display="https://etf.dws.com//en-gb/LU0942970442-esg-global-aggregate-bond-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B325:B325" r:id="R5bba6fba740e4744" display="https://etf.dws.com//en-gb/LU0942970798-esg-global-aggregate-bond-ucits-etf-5c-eur-hedged/"/>
+    <x:hyperlink ref="B326:B326" r:id="R779f7da5bd6c4116" display="https://etf.dws.com//en-gb/LU0943504760-switzerland-ucits-etf-1c/"/>
+    <x:hyperlink ref="B327:B327" r:id="Rb00537f687b24715" display="https://etf.dws.com//en-gb/LU0952581584-japan-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B328:B328" r:id="R2704189f2b9f40dc" display="https://etf.dws.com//en-gb/LU0962071741-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1d/"/>
+    <x:hyperlink ref="B329:B329" r:id="Rea329f72126b4536" display="https://etf.dws.com//en-gb/LU0962078753-global-inflation-linked-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B330:B330" r:id="R13e5f6b791a04e69" display="https://etf.dws.com//en-gb/LU0994505336-spain-ucits-etf-1d/"/>
+    <x:hyperlink ref="B331:B331" r:id="Reca8359bf5974af1" display="https://etf.dws.com//en-gb/LU1094612022-harvest-china-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B332:B332" r:id="R09af98a20d2d4937" display="https://etf.dws.com//en-gb/LU1109939865-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1d/"/>
+    <x:hyperlink ref="B333:B333" r:id="Rb31e6326fa614eed" display="https://etf.dws.com//en-gb/LU1109941689-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B334:B334" r:id="Rbf39e46206ae4f2f" display="https://etf.dws.com//en-gb/LU1109942653-eur-high-yield-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B335:B335" r:id="Ra783fc10830a43bb" display="https://etf.dws.com//en-gb/LU1109943388-eur-high-yield-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B336:B336" r:id="R1ca19338e4df4c85" display="https://etf.dws.com//en-gb/LU1127514245-msci-emu-ucits-etf-1c-usd-hedged/"/>
+    <x:hyperlink ref="B337:B337" r:id="Rd0e8d415b6634bf0" display="https://etf.dws.com//en-gb/LU1127516455-msci-emu-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B338:B338" r:id="Rb56d83df3e8e4a3d" display="https://etf.dws.com//en-gb/LU1184092051-msci-europe-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B339:B339" r:id="Reae3b0d23e9f4846" display="https://etf.dws.com//en-gb/LU1215827756-msci-japan-ucits-etf-7c-chf-hedged/"/>
+    <x:hyperlink ref="B340:B340" r:id="Rebdf574d8b804af8" display="https://etf.dws.com//en-gb/LU1215828218-msci-emu-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B341:B341" r:id="R3b98bc3d645a4013" display="https://etf.dws.com//en-gb/LU1221100792-dax-esg-screened-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B342:B342" r:id="Rfd2615cd742247fe" display="https://etf.dws.com//en-gb/LU1221102491-dax-esg-screened-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B343:B343" r:id="R51b02a5cad8043b4" display="https://etf.dws.com//en-gb/LU1242369327-msci-europe-ucits-etf-1d/"/>
+    <x:hyperlink ref="B344:B344" r:id="R8f8af243a9a14403" display="https://etf.dws.com//en-gb/LU1310477036-harvest-csi-a500-ucits-etf-1d/"/>
+    <x:hyperlink ref="B345:B345" r:id="Rbb755258e3b7436d" display="https://etf.dws.com//en-gb/LU1349386927-dax-ucits-etf-1d/"/>
+    <x:hyperlink ref="B346:B346" r:id="R162d9841ebb845fa" display="https://etf.dws.com//en-gb/LU1399300455-us-treasuries-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B347:B347" r:id="R5fefbd381c8d40d3" display="https://etf.dws.com//en-gb/LU1772333404-stoxx-europe-600-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B348:B348" r:id="Re516eee0622e4ed6" display="https://etf.dws.com//en-gb/LU1875395870-nikkei-225-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B349:B349" r:id="Racba0dbb83774b3a" display="https://etf.dws.com//en-gb/LU1920015440-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2c/"/>
+    <x:hyperlink ref="B350:B350" r:id="Rd81e8e91f93f410f" display="https://etf.dws.com//en-gb/LU1920015523-us-treasuries-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B351:B351" r:id="R902b9d5ff5934430" display="https://etf.dws.com//en-gb/LU1920015796-us-treasuries-ucits-etf-1c/"/>
+    <x:hyperlink ref="B352:B352" r:id="R8dd56d2fdf5d469b" display="https://etf.dws.com//en-gb/LU2009147591-eurozone-government-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B353:B353" r:id="R2f5ff06d62494083" display="https://etf.dws.com//en-gb/LU2009147757-s-p-500-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B354:B354" r:id="Rf069463c90c94d5d" display="https://etf.dws.com//en-gb/LU2158769930-j-p-morgan-em-local-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B355:B355" r:id="Red2598619fcf4240" display="https://etf.dws.com//en-gb/LU2178481649-eur-corporate-bond-short-duration-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B356:B356" r:id="Rc39036005c8d4a9d" display="https://etf.dws.com//en-gb/LU2196470426-nikkei-225-ucits-etf-1c/"/>
+    <x:hyperlink ref="B357:B357" r:id="R9038c5db94d0460e" display="https://etf.dws.com//en-gb/LU2196472984-s-p-500-swap-ucits-etf-5c-eur-hedged/"/>
+    <x:hyperlink ref="B358:B358" r:id="R1c04fb6c8ee44e77" display="https://etf.dws.com//en-gb/LU2196473016-s-p-500-swap-ucits-etf-7c-gbp-hedged/"/>
+    <x:hyperlink ref="B359:B359" r:id="R5b9c42873aa34234" display="https://etf.dws.com//en-gb/LU2263803533-msci-world-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B360:B360" r:id="Rd969b4744d1e4203" display="https://etf.dws.com//en-gb/LU2278080713-bloomberg-commodity-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B361:B361" r:id="R1757cc8fc72942af" display="https://etf.dws.com//en-gb/LU2296661775-msci-em-asia-screened-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B362:B362" r:id="R51b88c76e7cb40e3" display="https://etf.dws.com//en-gb/LU2361257269-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B363:B363" r:id="Re60024769fb2479a" display="https://etf.dws.com//en-gb/LU2376679564-harvest-msci-china-tech-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B364:B364" r:id="Rab235616a2ed4114" display="https://etf.dws.com//en-gb/LU2385068163-esg-global-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B365:B365" r:id="Rfcbf85fc32c442f1" display="https://etf.dws.com//en-gb/LU2385068247-esg-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B366:B366" r:id="R10d763b1b6b04e56" display="https://etf.dws.com//en-gb/LU2385068320-esg-global-government-bond-ucits-etf-3d-usd-hedged/"/>
+    <x:hyperlink ref="B367:B367" r:id="R87aa70dcd372492f" display="https://etf.dws.com//en-gb/LU2385068593-esg-global-government-bond-ucits-etf-4d-eur-hedged/"/>
+    <x:hyperlink ref="B368:B368" r:id="Re03c937cce6648ce" display="https://etf.dws.com//en-gb/LU2456436083-msci-china-ucits-etf-1d/"/>
+    <x:hyperlink ref="B369:B369" r:id="Rb1ce3c460f65447a" display="https://etf.dws.com//en-gb/LU2462217071-esg-global-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B370:B370" r:id="R75a49817533344b6" display="https://etf.dws.com//en-gb/LU2468423459-esg-eurozone-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B371:B371" r:id="R608aae85d9a14074" display="https://etf.dws.com//en-gb/LU2469465822-msci-china-a-screened-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B372:B372" r:id="Rc469f1c2c51e46e0" display="https://etf.dws.com//en-gb/LU2504532131-tips-us-inflation-linked-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B373:B373" r:id="R6895bcbff2a94449" display="https://etf.dws.com//en-gb/LU2504532487-eurozone-government-green-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B374:B374" r:id="Rcec91d44f1be4a17" display="https://etf.dws.com//en-gb/LU2504537445-eurozone-government-bond-esg-tilted-ucits-etf-1d/"/>
+    <x:hyperlink ref="B375:B375" r:id="Ra51420470683413a" display="https://etf.dws.com//en-gb/LU2523865728-eurozone-government-bond-7-10-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B376:B376" r:id="Rc8088abfc9e74898" display="https://etf.dws.com//en-gb/LU2523865991-eurozone-government-bond-7-10-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B377:B377" r:id="R4a5108a469ec4185" display="https://etf.dws.com//en-gb/LU2523866023-eurozone-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B378:B378" r:id="R58eea9e7a6104248" display="https://etf.dws.com//en-gb/LU2523866296-germany-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B379:B379" r:id="Rdf2940feb5bf43ae" display="https://etf.dws.com//en-gb/LU2523866379-germany-government-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B380:B380" r:id="R895178d57e95489d" display="https://etf.dws.com//en-gb/LU2552296563-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-2d/"/>
+    <x:hyperlink ref="B381:B381" r:id="R91490aabf0d14aa0" display="https://etf.dws.com//en-gb/LU2581375073-msci-usa-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B382:B382" r:id="R447dc139f7f84239" display="https://etf.dws.com//en-gb/LU2581375156-stoxx-europe-600-ucits-etf-1d/"/>
+    <x:hyperlink ref="B383:B383" r:id="R11a9617e99354d09" display="https://etf.dws.com//en-gb/LU2581375230-msci-japan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B384:B384" r:id="Re13d21dd8c904ddd" display="https://etf.dws.com//en-gb/LU2606231335-eurozone-government-bond-3-5-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B385:B385" r:id="R7ddafb97acc5456a" display="https://etf.dws.com//en-gb/LU2606231418-eurozone-government-bond-3-5-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B386:B386" r:id="R32c8e394ceb94a98" display="https://etf.dws.com//en-gb/LU2610432036-us-treasuries-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B387:B387" r:id="R0151f4f565594a75" display="https://etf.dws.com//en-gb/LU2641054122-eurozone-government-bond-0-1-ucits-etf-1c/"/>
+    <x:hyperlink ref="B388:B388" r:id="Ra46ecbe4db1b484d" display="https://etf.dws.com//en-gb/LU2641054551-germany-government-bond-0-1-ucits-etf-1c/"/>
+    <x:hyperlink ref="B389:B389" r:id="R151c3846707b4eed" display="https://etf.dws.com//en-gb/LU2662649412-us-treasuries-10-ucits-etf-1d/"/>
+    <x:hyperlink ref="B390:B390" r:id="R94332191c5e342f8" display="https://etf.dws.com//en-gb/LU2662649503-us-treasuries-3-7-ucits-etf-1d/"/>
+    <x:hyperlink ref="B391:B391" r:id="R009c4fabc3b74386" display="https://etf.dws.com//en-gb/LU2662649685-us-treasuries-7-10-ucits-etf-1d/"/>
+    <x:hyperlink ref="B392:B392" r:id="Ra31c0ed8237840c6" display="https://etf.dws.com//en-gb/LU2673522830-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B393:B393" r:id="R82f875529a37404b" display="https://etf.dws.com//en-gb/LU2673522913-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B394:B394" r:id="Rebcdbc3b07934812" display="https://etf.dws.com//en-gb/LU2673523051-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B395:B395" r:id="R57f2c0aaca8940da" display="https://etf.dws.com//en-gb/LU2673523135-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B396:B396" r:id="Rd26e720868834d19" display="https://etf.dws.com//en-gb/LU2673523218-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B397:B397" r:id="R916745ca81e746f8" display="https://etf.dws.com//en-gb/LU2673523309-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B398:B398" r:id="Re3eb5a4109e344e2" display="https://etf.dws.com//en-gb/LU2673523481-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B399:B399" r:id="Rbaa093a9e46f42ab" display="https://etf.dws.com//en-gb/LU2673523564-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B400:B400" r:id="R3a2a03c75b83418f" display="https://etf.dws.com//en-gb/LU2675291913-msci-emerging-markets-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B401:B401" r:id="Rda5ae2308112493e" display="https://etf.dws.com//en-gb/LU2755521270-msci-pacific-ex-japan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B402:B402" r:id="R8319377b2ccf4d7a" display="https://etf.dws.com//en-gb/LU2788421340-csi500-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B403:B403" r:id="R4698906594884ccc" display="https://etf.dws.com//en-gb/LU2809864296-target-maturity-sept-2030-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B404:B404" r:id="Ree1acad3852f41de" display="https://etf.dws.com//en-gb/LU2809864452-target-maturity-sept-2032-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B405:B405" r:id="Rf3d5d590a97e4b81" display="https://etf.dws.com//en-gb/LU2809864619-target-maturity-sept-2034-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B406:B406" r:id="R5c2724494b9d403b" display="https://etf.dws.com//en-gb/LU2810185665-target-maturity-sept-2028-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B407:B407" r:id="Rbb56b48695c2417f" display="https://etf.dws.com//en-gb/LU2859297330-world-small-cap-green-tech-innovators-ucits-etf-1c/"/>
+    <x:hyperlink ref="B408:B408" r:id="R635521ace2a74892" display="https://etf.dws.com//en-gb/LU2859392081-world-green-tech-innovators-ucits-etf-1c/"/>
+    <x:hyperlink ref="B409:B409" r:id="Rf3a69af688ed4473" display="https://etf.dws.com//en-gb/LU2903252349-scalable-msci-ac-world-xtrackers-ucits-etf-1c/"/>
+    <x:hyperlink ref="B410:B410" r:id="R40b9d870559b431d" display="https://etf.dws.com//en-gb/LU2928641757-msci-taiwan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B411:B411" r:id="Rd61707d3a5134c5b" display="https://etf.dws.com//en-gb/LU3003217554-eurozone-government-bond-1-3-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B412:B412" r:id="Rc40872eebbea480c" display="https://etf.dws.com//en-gb/LU3003217638-eurozone-government-bond-1-3-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B413:B413" r:id="R905e67bd5a0c41ab" display="https://etf.dws.com//en-gb/LU3003217711-eurozone-government-bond-5-7-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B414:B414" r:id="Rcafa72f9ce4d4ac0" display="https://etf.dws.com//en-gb/LU3003217984-eurozone-government-bond-5-7-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B415:B415" r:id="R5b61e86c87ee4af0" display="https://etf.dws.com//en-gb/LU3003218016-australia-government-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B416:B416" r:id="R5ab46c61b2f340a6" display="https://etf.dws.com//en-gb/LU3003218107-australia-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B417:B417" r:id="R570ecb24dbb64274" display="https://etf.dws.com//en-gb/LU3003218362-australia-government-bond-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B418:B418" r:id="R19bc40de09304faf" display="https://etf.dws.com//en-gb/LU3003218446-japan-government-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B419:B419" r:id="R4113a0a8df064677" display="https://etf.dws.com//en-gb/LU3003218792-japan-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B420:B420" r:id="Rb7ea48d363444088" display="https://etf.dws.com//en-gb/LU3003218958-japan-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B421:B421" r:id="R74ea1b6839034f8a" display="https://etf.dws.com//en-gb/LU3061478973-europe-defence-technologies-ucits-etf-1c/"/>
+    <x:hyperlink ref="B422:B422" r:id="Ra8ecdd91c6b94695" display="https://etf.dws.com//en-gb/LU3116008346-diversified-portfolio-20-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B423:B423" r:id="Rf71f1a7b6edb4161" display="https://etf.dws.com//en-gb/LU3116008429-diversified-portfolio-40-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B424:B424" r:id="Rc749e379e2c646ae" display="https://etf.dws.com//en-gb/LU3116008692-diversified-portfolio-60-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B425:B425" r:id="R6bef32748bc84ca2" display="https://etf.dws.com//en-gb/LU3116008775-diversified-portfolio-80-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B426:B426" r:id="R3c24342d768f47e6" display="https://etf.dws.com//en-gb/LU3121019551-global-government-bond-ucits-etf-3d-chf-hedged/"/>
+    <x:hyperlink ref="B427:B427" r:id="Rc453b3646ede4188" display="https://etf.dws.com//en-gb/LU3123443510-salam-usd-global-aggregate-sukuk-ucits-etf-1d/"/>
+    <x:hyperlink ref="B428:B428" r:id="R263542314cba4ee6" display="https://etf.dws.com//en-gb/LU3184977026-msci-world-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B429:B429" r:id="R594281a4e7494815" display="https://etf.dws.com//en-gb/LU3184977299-msci-europe-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B430:B430" r:id="R24eb0b5dff5c4f5f" display="https://etf.dws.com//en-gb/LU3184977372-msci-usa-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B431:B431" r:id="R588e52779600495b" display="https://etf.dws.com//en-gb/LU3184977455-msci-emerging-markets-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B432:B432" r:id="Rcb7813c219784a02" display="https://etf.dws.com//en-gb/LU3184977612-s-p-500-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B433:B433" r:id="Rb845ec752bc24da1" display="https://etf.dws.com//en-gb/LU3184977703-ftse-100-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B434:B434" r:id="R32441152126c4d9b" display="https://etf.dws.com//en-gb/LU3198621024-s-p-500-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B435:B435" r:id="R285b6a985a164f3b" display="https://etf.dws.com//en-gb/LU3284391318-global-government-bond-ucits-etf-4d/"/>
+    <x:hyperlink ref="B436:B436" r:id="Re1e5ad0393ae4521" display="https://etf.dws.com//en-gb/LU3353962940-stoxx-europe-600-ucits-etf-ic-eur-unlisted/"/>
   </x:hyperlinks>
   <x:pageMargins left="0.17" right="0.17" top="0.17" bottom="0.17" header="0" footer="0.3"/>
   <x:pageSetup orientation="landscape"/>
   <x:drawing r:id="rId2"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Re7c8fa2df28c4d25"/>
+    <x:tablePart r:id="R2cb07d8fbcfb4c89"/>
   </x:tableParts>
 </x:worksheet>
 </file>